--- a/output/version3/test/20-10/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1062</v>
+        <v>949</v>
       </c>
       <c r="C2" t="n">
-        <v>985</v>
+        <v>806</v>
       </c>
       <c r="D2" t="n">
-        <v>855</v>
+        <v>1003</v>
       </c>
       <c r="E2" t="n">
-        <v>925</v>
+        <v>944</v>
       </c>
       <c r="F2" t="n">
-        <v>842</v>
+        <v>820</v>
       </c>
       <c r="G2" t="n">
-        <v>892</v>
+        <v>847</v>
       </c>
       <c r="H2" t="n">
-        <v>920</v>
+        <v>844</v>
       </c>
       <c r="I2" t="n">
-        <v>1007</v>
+        <v>969</v>
       </c>
       <c r="J2" t="n">
-        <v>897</v>
+        <v>970</v>
       </c>
       <c r="K2" t="n">
-        <v>821</v>
+        <v>1008</v>
       </c>
       <c r="L2" t="n">
-        <v>920.6</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>912</v>
+        <v>866</v>
       </c>
       <c r="C3" t="n">
-        <v>861</v>
+        <v>921</v>
       </c>
       <c r="D3" t="n">
-        <v>846</v>
+        <v>984</v>
       </c>
       <c r="E3" t="n">
-        <v>963</v>
+        <v>888</v>
       </c>
       <c r="F3" t="n">
-        <v>1002</v>
+        <v>921</v>
       </c>
       <c r="G3" t="n">
-        <v>841</v>
+        <v>850</v>
       </c>
       <c r="H3" t="n">
-        <v>886</v>
+        <v>923</v>
       </c>
       <c r="I3" t="n">
-        <v>853</v>
+        <v>920</v>
       </c>
       <c r="J3" t="n">
-        <v>908</v>
+        <v>984</v>
       </c>
       <c r="K3" t="n">
-        <v>934</v>
+        <v>910</v>
       </c>
       <c r="L3" t="n">
-        <v>900.6</v>
+        <v>916.7</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>979</v>
+        <v>953</v>
       </c>
       <c r="C4" t="n">
-        <v>913</v>
+        <v>872</v>
       </c>
       <c r="D4" t="n">
-        <v>752</v>
+        <v>1050</v>
       </c>
       <c r="E4" t="n">
-        <v>824</v>
+        <v>963</v>
       </c>
       <c r="F4" t="n">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="G4" t="n">
-        <v>959</v>
+        <v>1011</v>
       </c>
       <c r="H4" t="n">
-        <v>875</v>
+        <v>810</v>
       </c>
       <c r="I4" t="n">
-        <v>856</v>
+        <v>797</v>
       </c>
       <c r="J4" t="n">
-        <v>871</v>
+        <v>921</v>
       </c>
       <c r="K4" t="n">
-        <v>762</v>
+        <v>1035</v>
       </c>
       <c r="L4" t="n">
-        <v>868.3</v>
+        <v>931.7</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>845</v>
+        <v>818</v>
       </c>
       <c r="C5" t="n">
-        <v>868</v>
+        <v>793</v>
       </c>
       <c r="D5" t="n">
-        <v>947</v>
+        <v>766</v>
       </c>
       <c r="E5" t="n">
-        <v>793</v>
+        <v>811</v>
       </c>
       <c r="F5" t="n">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="G5" t="n">
-        <v>772</v>
+        <v>928</v>
       </c>
       <c r="H5" t="n">
-        <v>956</v>
+        <v>815</v>
       </c>
       <c r="I5" t="n">
-        <v>841</v>
+        <v>965</v>
       </c>
       <c r="J5" t="n">
-        <v>911</v>
+        <v>843</v>
       </c>
       <c r="K5" t="n">
-        <v>869</v>
+        <v>939</v>
       </c>
       <c r="L5" t="n">
-        <v>868.6</v>
+        <v>857.1</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>966</v>
+        <v>816</v>
       </c>
       <c r="C6" t="n">
-        <v>806</v>
+        <v>979</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>864</v>
       </c>
       <c r="E6" t="n">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="F6" t="n">
-        <v>908</v>
+        <v>718</v>
       </c>
       <c r="G6" t="n">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="H6" t="n">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="I6" t="n">
-        <v>860</v>
+        <v>843</v>
       </c>
       <c r="J6" t="n">
-        <v>835</v>
+        <v>909</v>
       </c>
       <c r="K6" t="n">
-        <v>888</v>
+        <v>917</v>
       </c>
       <c r="L6" t="n">
-        <v>877.2</v>
+        <v>864.2</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>983</v>
+        <v>822</v>
       </c>
       <c r="C7" t="n">
-        <v>875</v>
+        <v>927</v>
       </c>
       <c r="D7" t="n">
-        <v>838</v>
+        <v>800</v>
       </c>
       <c r="E7" t="n">
-        <v>757</v>
+        <v>801</v>
       </c>
       <c r="F7" t="n">
-        <v>877</v>
+        <v>886</v>
       </c>
       <c r="G7" t="n">
-        <v>788</v>
+        <v>889</v>
       </c>
       <c r="H7" t="n">
-        <v>844</v>
+        <v>921</v>
       </c>
       <c r="I7" t="n">
-        <v>851</v>
+        <v>946</v>
       </c>
       <c r="J7" t="n">
-        <v>817</v>
+        <v>884</v>
       </c>
       <c r="K7" t="n">
-        <v>832</v>
+        <v>857</v>
       </c>
       <c r="L7" t="n">
-        <v>846.2</v>
+        <v>873.3</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>808</v>
+        <v>951</v>
       </c>
       <c r="C8" t="n">
-        <v>851</v>
+        <v>986</v>
       </c>
       <c r="D8" t="n">
-        <v>882</v>
+        <v>918</v>
       </c>
       <c r="E8" t="n">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F8" t="n">
-        <v>894</v>
+        <v>937</v>
       </c>
       <c r="G8" t="n">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="H8" t="n">
-        <v>873</v>
+        <v>946</v>
       </c>
       <c r="I8" t="n">
-        <v>917</v>
+        <v>945</v>
       </c>
       <c r="J8" t="n">
-        <v>851</v>
+        <v>972</v>
       </c>
       <c r="K8" t="n">
-        <v>874</v>
+        <v>965</v>
       </c>
       <c r="L8" t="n">
-        <v>871.7</v>
+        <v>938.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>918</v>
+        <v>822</v>
       </c>
       <c r="C9" t="n">
-        <v>814</v>
+        <v>892</v>
       </c>
       <c r="D9" t="n">
-        <v>841</v>
+        <v>888</v>
       </c>
       <c r="E9" t="n">
-        <v>791</v>
+        <v>759</v>
       </c>
       <c r="F9" t="n">
-        <v>978</v>
+        <v>872</v>
       </c>
       <c r="G9" t="n">
-        <v>835</v>
+        <v>959</v>
       </c>
       <c r="H9" t="n">
-        <v>1068</v>
+        <v>881</v>
       </c>
       <c r="I9" t="n">
-        <v>1041</v>
+        <v>884</v>
       </c>
       <c r="J9" t="n">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="K9" t="n">
-        <v>914</v>
+        <v>1055</v>
       </c>
       <c r="L9" t="n">
-        <v>907.5</v>
+        <v>888.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1004</v>
+        <v>817</v>
       </c>
       <c r="C10" t="n">
-        <v>924</v>
+        <v>854</v>
       </c>
       <c r="D10" t="n">
-        <v>858</v>
+        <v>822</v>
       </c>
       <c r="E10" t="n">
-        <v>875</v>
+        <v>708</v>
       </c>
       <c r="F10" t="n">
-        <v>796</v>
+        <v>749</v>
       </c>
       <c r="G10" t="n">
-        <v>852</v>
+        <v>797</v>
       </c>
       <c r="H10" t="n">
-        <v>965</v>
+        <v>794</v>
       </c>
       <c r="I10" t="n">
-        <v>1025</v>
+        <v>786</v>
       </c>
       <c r="J10" t="n">
-        <v>906</v>
+        <v>826</v>
       </c>
       <c r="K10" t="n">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="L10" t="n">
-        <v>904.6</v>
+        <v>800.2</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>832</v>
+        <v>904</v>
       </c>
       <c r="C11" t="n">
-        <v>768</v>
+        <v>845</v>
       </c>
       <c r="D11" t="n">
-        <v>894</v>
+        <v>771</v>
       </c>
       <c r="E11" t="n">
-        <v>767</v>
+        <v>870</v>
       </c>
       <c r="F11" t="n">
-        <v>828</v>
+        <v>788</v>
       </c>
       <c r="G11" t="n">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="H11" t="n">
-        <v>809</v>
+        <v>732</v>
       </c>
       <c r="I11" t="n">
-        <v>808</v>
+        <v>754</v>
       </c>
       <c r="J11" t="n">
-        <v>746</v>
+        <v>1014</v>
       </c>
       <c r="K11" t="n">
-        <v>909</v>
+        <v>816</v>
       </c>
       <c r="L11" t="n">
-        <v>810.9</v>
+        <v>824.9</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="C12" t="n">
-        <v>964</v>
+        <v>904</v>
       </c>
       <c r="D12" t="n">
-        <v>891</v>
+        <v>920</v>
       </c>
       <c r="E12" t="n">
-        <v>807</v>
+        <v>843</v>
       </c>
       <c r="F12" t="n">
-        <v>845</v>
+        <v>911</v>
       </c>
       <c r="G12" t="n">
-        <v>792</v>
+        <v>957</v>
       </c>
       <c r="H12" t="n">
-        <v>852</v>
+        <v>887</v>
       </c>
       <c r="I12" t="n">
-        <v>855</v>
+        <v>811</v>
       </c>
       <c r="J12" t="n">
-        <v>902</v>
+        <v>876</v>
       </c>
       <c r="K12" t="n">
-        <v>892</v>
+        <v>856</v>
       </c>
       <c r="L12" t="n">
-        <v>860.9</v>
+        <v>878.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>878</v>
+        <v>815</v>
       </c>
       <c r="C13" t="n">
-        <v>941</v>
+        <v>795</v>
       </c>
       <c r="D13" t="n">
-        <v>963</v>
+        <v>1027</v>
       </c>
       <c r="E13" t="n">
-        <v>894</v>
+        <v>743</v>
       </c>
       <c r="F13" t="n">
-        <v>860</v>
+        <v>780</v>
       </c>
       <c r="G13" t="n">
-        <v>930</v>
+        <v>868</v>
       </c>
       <c r="H13" t="n">
-        <v>924</v>
+        <v>902</v>
       </c>
       <c r="I13" t="n">
+        <v>1019</v>
+      </c>
+      <c r="J13" t="n">
+        <v>866</v>
+      </c>
+      <c r="K13" t="n">
         <v>788</v>
       </c>
-      <c r="J13" t="n">
-        <v>794</v>
-      </c>
-      <c r="K13" t="n">
-        <v>994</v>
-      </c>
       <c r="L13" t="n">
-        <v>896.6</v>
+        <v>860.3</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>847</v>
+        <v>964</v>
       </c>
       <c r="C14" t="n">
-        <v>918</v>
+        <v>946</v>
       </c>
       <c r="D14" t="n">
-        <v>911</v>
+        <v>886</v>
       </c>
       <c r="E14" t="n">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="F14" t="n">
-        <v>903</v>
+        <v>859</v>
       </c>
       <c r="G14" t="n">
-        <v>925</v>
+        <v>996</v>
       </c>
       <c r="H14" t="n">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="I14" t="n">
-        <v>831</v>
+        <v>876</v>
       </c>
       <c r="J14" t="n">
-        <v>889</v>
+        <v>937</v>
       </c>
       <c r="K14" t="n">
-        <v>939</v>
+        <v>1028</v>
       </c>
       <c r="L14" t="n">
-        <v>883.5</v>
+        <v>915.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="C15" t="n">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="D15" t="n">
-        <v>967</v>
+        <v>893</v>
       </c>
       <c r="E15" t="n">
-        <v>939</v>
+        <v>803</v>
       </c>
       <c r="F15" t="n">
-        <v>962</v>
+        <v>897</v>
       </c>
       <c r="G15" t="n">
-        <v>872</v>
+        <v>889</v>
       </c>
       <c r="H15" t="n">
-        <v>1058</v>
+        <v>1002</v>
       </c>
       <c r="I15" t="n">
-        <v>944</v>
+        <v>1044</v>
       </c>
       <c r="J15" t="n">
-        <v>914</v>
+        <v>871</v>
       </c>
       <c r="K15" t="n">
-        <v>904</v>
+        <v>856</v>
       </c>
       <c r="L15" t="n">
-        <v>930.2</v>
+        <v>897.4</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C16" t="n">
-        <v>949</v>
+        <v>859</v>
       </c>
       <c r="D16" t="n">
-        <v>896</v>
+        <v>1091</v>
       </c>
       <c r="E16" t="n">
-        <v>872</v>
+        <v>952</v>
       </c>
       <c r="F16" t="n">
-        <v>850</v>
+        <v>815</v>
       </c>
       <c r="G16" t="n">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="H16" t="n">
-        <v>819</v>
+        <v>911</v>
       </c>
       <c r="I16" t="n">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="J16" t="n">
-        <v>915</v>
+        <v>756</v>
       </c>
       <c r="K16" t="n">
-        <v>830</v>
+        <v>931</v>
       </c>
       <c r="L16" t="n">
-        <v>865.3</v>
+        <v>890.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>752</v>
+        <v>879</v>
       </c>
       <c r="C17" t="n">
-        <v>839</v>
+        <v>875</v>
       </c>
       <c r="D17" t="n">
-        <v>797</v>
+        <v>870</v>
       </c>
       <c r="E17" t="n">
-        <v>841</v>
+        <v>776</v>
       </c>
       <c r="F17" t="n">
-        <v>737</v>
+        <v>787</v>
       </c>
       <c r="G17" t="n">
-        <v>791</v>
+        <v>825</v>
       </c>
       <c r="H17" t="n">
-        <v>776</v>
+        <v>918</v>
       </c>
       <c r="I17" t="n">
-        <v>740</v>
+        <v>704</v>
       </c>
       <c r="J17" t="n">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="K17" t="n">
-        <v>670</v>
+        <v>887</v>
       </c>
       <c r="L17" t="n">
-        <v>767.9</v>
+        <v>824.8</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1003</v>
+        <v>922</v>
       </c>
       <c r="C18" t="n">
-        <v>880</v>
+        <v>847</v>
       </c>
       <c r="D18" t="n">
-        <v>925</v>
+        <v>989</v>
       </c>
       <c r="E18" t="n">
-        <v>1033</v>
+        <v>859</v>
       </c>
       <c r="F18" t="n">
-        <v>1015</v>
+        <v>926</v>
       </c>
       <c r="G18" t="n">
-        <v>878</v>
+        <v>855</v>
       </c>
       <c r="H18" t="n">
-        <v>957</v>
+        <v>973</v>
       </c>
       <c r="I18" t="n">
-        <v>919</v>
+        <v>1010</v>
       </c>
       <c r="J18" t="n">
-        <v>945</v>
+        <v>881</v>
       </c>
       <c r="K18" t="n">
         <v>892</v>
       </c>
       <c r="L18" t="n">
-        <v>944.7</v>
+        <v>915.4</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>757</v>
+        <v>773</v>
       </c>
       <c r="C19" t="n">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="D19" t="n">
-        <v>794</v>
+        <v>980</v>
       </c>
       <c r="E19" t="n">
-        <v>698</v>
+        <v>906</v>
       </c>
       <c r="F19" t="n">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="G19" t="n">
-        <v>749</v>
+        <v>834</v>
       </c>
       <c r="H19" t="n">
-        <v>840</v>
+        <v>736</v>
       </c>
       <c r="I19" t="n">
-        <v>787</v>
+        <v>915</v>
       </c>
       <c r="J19" t="n">
-        <v>811</v>
+        <v>786</v>
       </c>
       <c r="K19" t="n">
-        <v>736</v>
+        <v>843</v>
       </c>
       <c r="L19" t="n">
-        <v>777.8</v>
+        <v>838</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>738</v>
+        <v>839</v>
       </c>
       <c r="C20" t="n">
-        <v>764</v>
+        <v>733</v>
       </c>
       <c r="D20" t="n">
-        <v>838</v>
+        <v>884</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>729</v>
       </c>
       <c r="F20" t="n">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G20" t="n">
-        <v>744</v>
+        <v>796</v>
       </c>
       <c r="H20" t="n">
-        <v>747</v>
+        <v>725</v>
       </c>
       <c r="I20" t="n">
-        <v>761</v>
+        <v>908</v>
       </c>
       <c r="J20" t="n">
-        <v>891</v>
+        <v>759</v>
       </c>
       <c r="K20" t="n">
-        <v>753</v>
+        <v>874</v>
       </c>
       <c r="L20" t="n">
-        <v>788.9</v>
+        <v>809.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
+        <v>915</v>
+      </c>
+      <c r="C21" t="n">
+        <v>936</v>
+      </c>
+      <c r="D21" t="n">
+        <v>939</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1007</v>
+      </c>
+      <c r="G21" t="n">
         <v>837</v>
       </c>
-      <c r="C21" t="n">
-        <v>1001</v>
-      </c>
-      <c r="D21" t="n">
-        <v>996</v>
-      </c>
-      <c r="E21" t="n">
-        <v>902</v>
-      </c>
-      <c r="F21" t="n">
-        <v>890</v>
-      </c>
-      <c r="G21" t="n">
-        <v>910</v>
-      </c>
       <c r="H21" t="n">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I21" t="n">
-        <v>983</v>
+        <v>928</v>
       </c>
       <c r="J21" t="n">
-        <v>937</v>
+        <v>855</v>
       </c>
       <c r="K21" t="n">
-        <v>903</v>
+        <v>965</v>
       </c>
       <c r="L21" t="n">
-        <v>937.5</v>
+        <v>944.3</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>831</v>
+        <v>782</v>
       </c>
       <c r="C22" t="n">
-        <v>868</v>
+        <v>949</v>
       </c>
       <c r="D22" t="n">
-        <v>836</v>
+        <v>763</v>
       </c>
       <c r="E22" t="n">
-        <v>831</v>
+        <v>914</v>
       </c>
       <c r="F22" t="n">
-        <v>885</v>
+        <v>952</v>
       </c>
       <c r="G22" t="n">
-        <v>903</v>
+        <v>799</v>
       </c>
       <c r="H22" t="n">
-        <v>887</v>
+        <v>873</v>
       </c>
       <c r="I22" t="n">
-        <v>890</v>
+        <v>817</v>
       </c>
       <c r="J22" t="n">
-        <v>744</v>
+        <v>893</v>
       </c>
       <c r="K22" t="n">
-        <v>939</v>
+        <v>926</v>
       </c>
       <c r="L22" t="n">
-        <v>861.4</v>
+        <v>866.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>855</v>
+        <v>1022</v>
       </c>
       <c r="C23" t="n">
-        <v>1028</v>
+        <v>757</v>
       </c>
       <c r="D23" t="n">
-        <v>934</v>
+        <v>1014</v>
       </c>
       <c r="E23" t="n">
-        <v>831</v>
+        <v>790</v>
       </c>
       <c r="F23" t="n">
-        <v>923</v>
+        <v>982</v>
       </c>
       <c r="G23" t="n">
-        <v>1028</v>
+        <v>814</v>
       </c>
       <c r="H23" t="n">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="I23" t="n">
-        <v>818</v>
+        <v>747</v>
       </c>
       <c r="J23" t="n">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="K23" t="n">
-        <v>895</v>
+        <v>986</v>
       </c>
       <c r="L23" t="n">
-        <v>906.5</v>
+        <v>889.6</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>759</v>
+        <v>859</v>
       </c>
       <c r="C24" t="n">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="D24" t="n">
-        <v>770</v>
+        <v>804</v>
       </c>
       <c r="E24" t="n">
-        <v>899</v>
+        <v>882</v>
       </c>
       <c r="F24" t="n">
-        <v>869</v>
+        <v>841</v>
       </c>
       <c r="G24" t="n">
-        <v>784</v>
+        <v>944</v>
       </c>
       <c r="H24" t="n">
-        <v>953</v>
+        <v>836</v>
       </c>
       <c r="I24" t="n">
-        <v>758</v>
+        <v>900</v>
       </c>
       <c r="J24" t="n">
-        <v>770</v>
+        <v>829</v>
       </c>
       <c r="K24" t="n">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="L24" t="n">
-        <v>835.1</v>
+        <v>868.8</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>926</v>
+        <v>899</v>
       </c>
       <c r="C25" t="n">
-        <v>894</v>
+        <v>777</v>
       </c>
       <c r="D25" t="n">
-        <v>1032</v>
+        <v>907</v>
       </c>
       <c r="E25" t="n">
-        <v>1033</v>
+        <v>873</v>
       </c>
       <c r="F25" t="n">
-        <v>786</v>
+        <v>901</v>
       </c>
       <c r="G25" t="n">
-        <v>917</v>
+        <v>853</v>
       </c>
       <c r="H25" t="n">
-        <v>958</v>
+        <v>877</v>
       </c>
       <c r="I25" t="n">
-        <v>776</v>
+        <v>893</v>
       </c>
       <c r="J25" t="n">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="K25" t="n">
-        <v>837</v>
+        <v>989</v>
       </c>
       <c r="L25" t="n">
-        <v>904.7</v>
+        <v>886</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1012</v>
+        <v>934</v>
       </c>
       <c r="C26" t="n">
-        <v>1010</v>
+        <v>1032</v>
       </c>
       <c r="D26" t="n">
-        <v>940</v>
+        <v>1058</v>
       </c>
       <c r="E26" t="n">
-        <v>937</v>
+        <v>1074</v>
       </c>
       <c r="F26" t="n">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="G26" t="n">
-        <v>930</v>
+        <v>978</v>
       </c>
       <c r="H26" t="n">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I26" t="n">
-        <v>1040</v>
+        <v>919</v>
       </c>
       <c r="J26" t="n">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="K26" t="n">
-        <v>968</v>
+        <v>1080</v>
       </c>
       <c r="L26" t="n">
-        <v>974.2</v>
+        <v>992.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>840</v>
+        <v>947</v>
       </c>
       <c r="C27" t="n">
+        <v>931</v>
+      </c>
+      <c r="D27" t="n">
+        <v>999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>854</v>
+      </c>
+      <c r="F27" t="n">
+        <v>883</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1038</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1047</v>
+      </c>
+      <c r="I27" t="n">
+        <v>916</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1089</v>
+      </c>
+      <c r="K27" t="n">
         <v>952</v>
       </c>
-      <c r="D27" t="n">
-        <v>959</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1004</v>
-      </c>
-      <c r="F27" t="n">
-        <v>988</v>
-      </c>
-      <c r="G27" t="n">
-        <v>820</v>
-      </c>
-      <c r="H27" t="n">
-        <v>928</v>
-      </c>
-      <c r="I27" t="n">
-        <v>913</v>
-      </c>
-      <c r="J27" t="n">
-        <v>978</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1063</v>
-      </c>
       <c r="L27" t="n">
-        <v>944.5</v>
+        <v>965.6</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>824</v>
+        <v>871</v>
       </c>
       <c r="C28" t="n">
+        <v>890</v>
+      </c>
+      <c r="D28" t="n">
         <v>856</v>
       </c>
-      <c r="D28" t="n">
-        <v>748</v>
-      </c>
       <c r="E28" t="n">
-        <v>977</v>
+        <v>934</v>
       </c>
       <c r="F28" t="n">
-        <v>763</v>
+        <v>804</v>
       </c>
       <c r="G28" t="n">
-        <v>846</v>
+        <v>750</v>
       </c>
       <c r="H28" t="n">
-        <v>841</v>
+        <v>770</v>
       </c>
       <c r="I28" t="n">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="J28" t="n">
-        <v>736</v>
+        <v>773</v>
       </c>
       <c r="K28" t="n">
-        <v>730</v>
+        <v>902</v>
       </c>
       <c r="L28" t="n">
-        <v>811.3</v>
+        <v>837.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>842</v>
+        <v>880</v>
       </c>
       <c r="C29" t="n">
-        <v>871</v>
+        <v>815</v>
       </c>
       <c r="D29" t="n">
-        <v>726</v>
+        <v>846</v>
       </c>
       <c r="E29" t="n">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F29" t="n">
-        <v>919</v>
+        <v>779</v>
       </c>
       <c r="G29" t="n">
-        <v>778</v>
+        <v>854</v>
       </c>
       <c r="H29" t="n">
-        <v>924</v>
+        <v>874</v>
       </c>
       <c r="I29" t="n">
-        <v>852</v>
+        <v>809</v>
       </c>
       <c r="J29" t="n">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K29" t="n">
-        <v>904</v>
+        <v>869</v>
       </c>
       <c r="L29" t="n">
-        <v>849.3</v>
+        <v>839.8</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>828</v>
+        <v>841</v>
       </c>
       <c r="C30" t="n">
-        <v>791</v>
+        <v>836</v>
       </c>
       <c r="D30" t="n">
-        <v>846</v>
+        <v>1014</v>
       </c>
       <c r="E30" t="n">
-        <v>714</v>
+        <v>766</v>
       </c>
       <c r="F30" t="n">
-        <v>838</v>
+        <v>808</v>
       </c>
       <c r="G30" t="n">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="H30" t="n">
-        <v>842</v>
+        <v>774</v>
       </c>
       <c r="I30" t="n">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="J30" t="n">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="K30" t="n">
-        <v>806</v>
+        <v>883</v>
       </c>
       <c r="L30" t="n">
-        <v>824.8</v>
+        <v>853.1</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>932</v>
+        <v>831</v>
       </c>
       <c r="C31" t="n">
-        <v>984</v>
+        <v>898</v>
       </c>
       <c r="D31" t="n">
-        <v>960</v>
+        <v>836</v>
       </c>
       <c r="E31" t="n">
         <v>967</v>
       </c>
       <c r="F31" t="n">
-        <v>942</v>
+        <v>885</v>
       </c>
       <c r="G31" t="n">
-        <v>986</v>
+        <v>922</v>
       </c>
       <c r="H31" t="n">
+        <v>949</v>
+      </c>
+      <c r="I31" t="n">
+        <v>971</v>
+      </c>
+      <c r="J31" t="n">
         <v>952</v>
       </c>
-      <c r="I31" t="n">
-        <v>893</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1050</v>
-      </c>
       <c r="K31" t="n">
-        <v>927</v>
+        <v>990</v>
       </c>
       <c r="L31" t="n">
-        <v>959.3</v>
+        <v>920.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>956</v>
+        <v>903</v>
       </c>
       <c r="C32" t="n">
-        <v>986</v>
+        <v>1085</v>
       </c>
       <c r="D32" t="n">
-        <v>954</v>
+        <v>910</v>
       </c>
       <c r="E32" t="n">
+        <v>1077</v>
+      </c>
+      <c r="F32" t="n">
+        <v>975</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1055</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1158</v>
+      </c>
+      <c r="J32" t="n">
+        <v>992</v>
+      </c>
+      <c r="K32" t="n">
         <v>1005</v>
       </c>
-      <c r="F32" t="n">
-        <v>991</v>
-      </c>
-      <c r="G32" t="n">
-        <v>946</v>
-      </c>
-      <c r="H32" t="n">
-        <v>944</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1014</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1055</v>
-      </c>
-      <c r="K32" t="n">
-        <v>910</v>
-      </c>
       <c r="L32" t="n">
-        <v>976.1</v>
+        <v>1023.6</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>890</v>
+        <v>1001</v>
       </c>
       <c r="C33" t="n">
-        <v>1044</v>
+        <v>939</v>
       </c>
       <c r="D33" t="n">
-        <v>824</v>
+        <v>959</v>
       </c>
       <c r="E33" t="n">
-        <v>890</v>
+        <v>913</v>
       </c>
       <c r="F33" t="n">
-        <v>826</v>
+        <v>858</v>
       </c>
       <c r="G33" t="n">
-        <v>794</v>
+        <v>867</v>
       </c>
       <c r="H33" t="n">
-        <v>846</v>
+        <v>821</v>
       </c>
       <c r="I33" t="n">
-        <v>881</v>
+        <v>854</v>
       </c>
       <c r="J33" t="n">
-        <v>804</v>
+        <v>904</v>
       </c>
       <c r="K33" t="n">
-        <v>873</v>
+        <v>992</v>
       </c>
       <c r="L33" t="n">
-        <v>867.2</v>
+        <v>910.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>989</v>
+        <v>1036</v>
       </c>
       <c r="C34" t="n">
-        <v>966</v>
+        <v>817</v>
       </c>
       <c r="D34" t="n">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="E34" t="n">
-        <v>929</v>
+        <v>893</v>
       </c>
       <c r="F34" t="n">
-        <v>1029</v>
+        <v>884</v>
       </c>
       <c r="G34" t="n">
-        <v>943</v>
+        <v>1054</v>
       </c>
       <c r="H34" t="n">
-        <v>962</v>
+        <v>858</v>
       </c>
       <c r="I34" t="n">
-        <v>1005</v>
+        <v>811</v>
       </c>
       <c r="J34" t="n">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="K34" t="n">
-        <v>1011</v>
+        <v>960</v>
       </c>
       <c r="L34" t="n">
-        <v>975.1</v>
+        <v>923.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="C35" t="n">
-        <v>896</v>
+        <v>1019</v>
       </c>
       <c r="D35" t="n">
-        <v>905</v>
+        <v>955</v>
       </c>
       <c r="E35" t="n">
+        <v>912</v>
+      </c>
+      <c r="F35" t="n">
+        <v>946</v>
+      </c>
+      <c r="G35" t="n">
+        <v>844</v>
+      </c>
+      <c r="H35" t="n">
         <v>958</v>
       </c>
-      <c r="F35" t="n">
-        <v>855</v>
-      </c>
-      <c r="G35" t="n">
-        <v>912</v>
-      </c>
-      <c r="H35" t="n">
-        <v>872</v>
-      </c>
       <c r="I35" t="n">
-        <v>917</v>
+        <v>947</v>
       </c>
       <c r="J35" t="n">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="K35" t="n">
-        <v>849</v>
+        <v>909</v>
       </c>
       <c r="L35" t="n">
-        <v>887.4</v>
+        <v>922.4</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>951</v>
+        <v>819</v>
       </c>
       <c r="C36" t="n">
-        <v>929</v>
+        <v>812</v>
       </c>
       <c r="D36" t="n">
-        <v>853</v>
+        <v>893</v>
       </c>
       <c r="E36" t="n">
-        <v>948</v>
+        <v>963</v>
       </c>
       <c r="F36" t="n">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="G36" t="n">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="H36" t="n">
-        <v>841</v>
+        <v>946</v>
       </c>
       <c r="I36" t="n">
-        <v>941</v>
+        <v>1005</v>
       </c>
       <c r="J36" t="n">
-        <v>954</v>
+        <v>843</v>
       </c>
       <c r="K36" t="n">
-        <v>869</v>
+        <v>810</v>
       </c>
       <c r="L36" t="n">
-        <v>915.9</v>
+        <v>899</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>928</v>
+        <v>860</v>
       </c>
       <c r="C37" t="n">
-        <v>779</v>
+        <v>932</v>
       </c>
       <c r="D37" t="n">
-        <v>695</v>
+        <v>809</v>
       </c>
       <c r="E37" t="n">
-        <v>842</v>
+        <v>1056</v>
       </c>
       <c r="F37" t="n">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="G37" t="n">
-        <v>887</v>
+        <v>946</v>
       </c>
       <c r="H37" t="n">
-        <v>897</v>
+        <v>681</v>
       </c>
       <c r="I37" t="n">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="J37" t="n">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="K37" t="n">
-        <v>810</v>
+        <v>768</v>
       </c>
       <c r="L37" t="n">
-        <v>837.6</v>
+        <v>856.1</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C38" t="n">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="D38" t="n">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="E38" t="n">
-        <v>888</v>
+        <v>785</v>
       </c>
       <c r="F38" t="n">
-        <v>837</v>
+        <v>786</v>
       </c>
       <c r="G38" t="n">
-        <v>837</v>
+        <v>807</v>
       </c>
       <c r="H38" t="n">
-        <v>874</v>
+        <v>783</v>
       </c>
       <c r="I38" t="n">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="J38" t="n">
-        <v>829</v>
+        <v>925</v>
       </c>
       <c r="K38" t="n">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="L38" t="n">
-        <v>859</v>
+        <v>838</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="C39" t="n">
-        <v>838</v>
+        <v>984</v>
       </c>
       <c r="D39" t="n">
-        <v>889</v>
+        <v>998</v>
       </c>
       <c r="E39" t="n">
-        <v>866</v>
+        <v>896</v>
       </c>
       <c r="F39" t="n">
-        <v>782</v>
+        <v>805</v>
       </c>
       <c r="G39" t="n">
-        <v>886</v>
+        <v>938</v>
       </c>
       <c r="H39" t="n">
-        <v>817</v>
+        <v>987</v>
       </c>
       <c r="I39" t="n">
-        <v>903</v>
+        <v>862</v>
       </c>
       <c r="J39" t="n">
-        <v>867</v>
+        <v>826</v>
       </c>
       <c r="K39" t="n">
-        <v>844</v>
+        <v>874</v>
       </c>
       <c r="L39" t="n">
-        <v>845.2</v>
+        <v>896.4</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>766</v>
+        <v>829</v>
       </c>
       <c r="C40" t="n">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="D40" t="n">
-        <v>930</v>
+        <v>825</v>
       </c>
       <c r="E40" t="n">
-        <v>837</v>
+        <v>723</v>
       </c>
       <c r="F40" t="n">
-        <v>889</v>
+        <v>746</v>
       </c>
       <c r="G40" t="n">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="H40" t="n">
-        <v>836</v>
+        <v>895</v>
       </c>
       <c r="I40" t="n">
-        <v>874</v>
+        <v>745</v>
       </c>
       <c r="J40" t="n">
         <v>806</v>
       </c>
       <c r="K40" t="n">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="L40" t="n">
-        <v>842.1</v>
+        <v>801.4</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>833</v>
+        <v>713</v>
       </c>
       <c r="C41" t="n">
-        <v>721</v>
+        <v>793</v>
       </c>
       <c r="D41" t="n">
-        <v>961</v>
+        <v>757</v>
       </c>
       <c r="E41" t="n">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="F41" t="n">
-        <v>736</v>
+        <v>936</v>
       </c>
       <c r="G41" t="n">
-        <v>864</v>
+        <v>821</v>
       </c>
       <c r="H41" t="n">
-        <v>773</v>
+        <v>896</v>
       </c>
       <c r="I41" t="n">
-        <v>760</v>
+        <v>718</v>
       </c>
       <c r="J41" t="n">
-        <v>845</v>
+        <v>858</v>
       </c>
       <c r="K41" t="n">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="L41" t="n">
-        <v>807.8</v>
+        <v>810.1</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>886</v>
+        <v>992</v>
       </c>
       <c r="C42" t="n">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="D42" t="n">
-        <v>853</v>
+        <v>798</v>
       </c>
       <c r="E42" t="n">
-        <v>928</v>
+        <v>749</v>
       </c>
       <c r="F42" t="n">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="G42" t="n">
-        <v>714</v>
+        <v>926</v>
       </c>
       <c r="H42" t="n">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="I42" t="n">
-        <v>879</v>
+        <v>785</v>
       </c>
       <c r="J42" t="n">
-        <v>927</v>
+        <v>874</v>
       </c>
       <c r="K42" t="n">
-        <v>913</v>
+        <v>820</v>
       </c>
       <c r="L42" t="n">
-        <v>865.4</v>
+        <v>852.9</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>833</v>
+        <v>856</v>
       </c>
       <c r="C43" t="n">
-        <v>851</v>
+        <v>877</v>
       </c>
       <c r="D43" t="n">
-        <v>811</v>
+        <v>926</v>
       </c>
       <c r="E43" t="n">
-        <v>863</v>
+        <v>931</v>
       </c>
       <c r="F43" t="n">
-        <v>958</v>
+        <v>870</v>
       </c>
       <c r="G43" t="n">
-        <v>831</v>
+        <v>744</v>
       </c>
       <c r="H43" t="n">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="I43" t="n">
-        <v>863</v>
+        <v>832</v>
       </c>
       <c r="J43" t="n">
-        <v>837</v>
+        <v>883</v>
       </c>
       <c r="K43" t="n">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="L43" t="n">
-        <v>853.6</v>
+        <v>858.5</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>759</v>
+        <v>824</v>
       </c>
       <c r="C44" t="n">
-        <v>815</v>
+        <v>756</v>
       </c>
       <c r="D44" t="n">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="E44" t="n">
-        <v>715</v>
+        <v>753</v>
       </c>
       <c r="F44" t="n">
-        <v>710</v>
+        <v>756</v>
       </c>
       <c r="G44" t="n">
-        <v>814</v>
+        <v>714</v>
       </c>
       <c r="H44" t="n">
-        <v>712</v>
+        <v>928</v>
       </c>
       <c r="I44" t="n">
-        <v>852</v>
+        <v>962</v>
       </c>
       <c r="J44" t="n">
-        <v>831</v>
+        <v>783</v>
       </c>
       <c r="K44" t="n">
-        <v>731</v>
+        <v>772</v>
       </c>
       <c r="L44" t="n">
-        <v>768.6</v>
+        <v>797.7</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>990</v>
+        <v>871</v>
       </c>
       <c r="C45" t="n">
-        <v>1042</v>
+        <v>1051</v>
       </c>
       <c r="D45" t="n">
-        <v>946</v>
+        <v>1027</v>
       </c>
       <c r="E45" t="n">
-        <v>927</v>
+        <v>964</v>
       </c>
       <c r="F45" t="n">
-        <v>928</v>
+        <v>1048</v>
       </c>
       <c r="G45" t="n">
-        <v>909</v>
+        <v>1141</v>
       </c>
       <c r="H45" t="n">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="I45" t="n">
-        <v>899</v>
+        <v>986</v>
       </c>
       <c r="J45" t="n">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="K45" t="n">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="L45" t="n">
-        <v>966.8</v>
+        <v>1011.2</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>939</v>
+        <v>835</v>
       </c>
       <c r="C46" t="n">
-        <v>903</v>
+        <v>921</v>
       </c>
       <c r="D46" t="n">
-        <v>917</v>
+        <v>810</v>
       </c>
       <c r="E46" t="n">
+        <v>820</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1043</v>
+      </c>
+      <c r="G46" t="n">
+        <v>946</v>
+      </c>
+      <c r="H46" t="n">
+        <v>886</v>
+      </c>
+      <c r="I46" t="n">
         <v>943</v>
       </c>
-      <c r="F46" t="n">
-        <v>802</v>
-      </c>
-      <c r="G46" t="n">
-        <v>847</v>
-      </c>
-      <c r="H46" t="n">
-        <v>934</v>
-      </c>
-      <c r="I46" t="n">
-        <v>949</v>
-      </c>
       <c r="J46" t="n">
-        <v>969</v>
+        <v>842</v>
       </c>
       <c r="K46" t="n">
-        <v>861</v>
+        <v>914</v>
       </c>
       <c r="L46" t="n">
-        <v>906.4</v>
+        <v>896</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>908</v>
+        <v>958</v>
       </c>
       <c r="C47" t="n">
-        <v>922</v>
+        <v>850</v>
       </c>
       <c r="D47" t="n">
-        <v>1035</v>
+        <v>874</v>
       </c>
       <c r="E47" t="n">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="F47" t="n">
-        <v>838</v>
+        <v>873</v>
       </c>
       <c r="G47" t="n">
-        <v>1044</v>
+        <v>997</v>
       </c>
       <c r="H47" t="n">
-        <v>910</v>
+        <v>939</v>
       </c>
       <c r="I47" t="n">
-        <v>907</v>
+        <v>1087</v>
       </c>
       <c r="J47" t="n">
-        <v>957</v>
+        <v>936</v>
       </c>
       <c r="K47" t="n">
-        <v>929</v>
+        <v>970</v>
       </c>
       <c r="L47" t="n">
-        <v>941.7</v>
+        <v>944.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>899</v>
+        <v>746</v>
       </c>
       <c r="C48" t="n">
-        <v>731</v>
+        <v>824</v>
       </c>
       <c r="D48" t="n">
-        <v>798</v>
+        <v>716</v>
       </c>
       <c r="E48" t="n">
-        <v>840</v>
+        <v>692</v>
       </c>
       <c r="F48" t="n">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="G48" t="n">
-        <v>826</v>
+        <v>979</v>
       </c>
       <c r="H48" t="n">
-        <v>778</v>
+        <v>670</v>
       </c>
       <c r="I48" t="n">
-        <v>676</v>
+        <v>870</v>
       </c>
       <c r="J48" t="n">
-        <v>693</v>
+        <v>849</v>
       </c>
       <c r="K48" t="n">
-        <v>718</v>
+        <v>881</v>
       </c>
       <c r="L48" t="n">
-        <v>773.4</v>
+        <v>801.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>794</v>
+        <v>887</v>
       </c>
       <c r="C49" t="n">
-        <v>793</v>
+        <v>835</v>
       </c>
       <c r="D49" t="n">
-        <v>913</v>
+        <v>861</v>
       </c>
       <c r="E49" t="n">
-        <v>964</v>
+        <v>854</v>
       </c>
       <c r="F49" t="n">
-        <v>883</v>
+        <v>835</v>
       </c>
       <c r="G49" t="n">
-        <v>815</v>
+        <v>763</v>
       </c>
       <c r="H49" t="n">
-        <v>911</v>
+        <v>844</v>
       </c>
       <c r="I49" t="n">
-        <v>775</v>
+        <v>959</v>
       </c>
       <c r="J49" t="n">
-        <v>887</v>
+        <v>809</v>
       </c>
       <c r="K49" t="n">
-        <v>829</v>
+        <v>860</v>
       </c>
       <c r="L49" t="n">
-        <v>856.4</v>
+        <v>850.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="C50" t="n">
-        <v>918</v>
+        <v>778</v>
       </c>
       <c r="D50" t="n">
-        <v>941</v>
+        <v>757</v>
       </c>
       <c r="E50" t="n">
-        <v>949</v>
+        <v>852</v>
       </c>
       <c r="F50" t="n">
-        <v>1052</v>
+        <v>797</v>
       </c>
       <c r="G50" t="n">
-        <v>861</v>
+        <v>832</v>
       </c>
       <c r="H50" t="n">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="I50" t="n">
-        <v>882</v>
+        <v>856</v>
       </c>
       <c r="J50" t="n">
-        <v>933</v>
+        <v>849</v>
       </c>
       <c r="K50" t="n">
-        <v>898</v>
+        <v>856</v>
       </c>
       <c r="L50" t="n">
-        <v>920.6</v>
+        <v>832.7</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>904</v>
+        <v>791</v>
       </c>
       <c r="C51" t="n">
-        <v>878</v>
+        <v>809</v>
       </c>
       <c r="D51" t="n">
-        <v>862</v>
+        <v>885</v>
       </c>
       <c r="E51" t="n">
-        <v>847</v>
+        <v>774</v>
       </c>
       <c r="F51" t="n">
-        <v>905</v>
+        <v>933</v>
       </c>
       <c r="G51" t="n">
-        <v>876</v>
+        <v>928</v>
       </c>
       <c r="H51" t="n">
-        <v>746</v>
+        <v>913</v>
       </c>
       <c r="I51" t="n">
-        <v>952</v>
+        <v>859</v>
       </c>
       <c r="J51" t="n">
-        <v>829</v>
+        <v>892</v>
       </c>
       <c r="K51" t="n">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="L51" t="n">
-        <v>866.8</v>
+        <v>863</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>880.16</v>
+        <v>873.34</v>
       </c>
       <c r="C52" t="n">
-        <v>890.9</v>
+        <v>881.38</v>
       </c>
       <c r="D52" t="n">
-        <v>878.8</v>
+        <v>893.38</v>
       </c>
       <c r="E52" t="n">
-        <v>880.72</v>
+        <v>864.5</v>
       </c>
       <c r="F52" t="n">
-        <v>874.8</v>
+        <v>865.4400000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>857.86</v>
+        <v>884.66</v>
       </c>
       <c r="H52" t="n">
-        <v>885.22</v>
+        <v>878.12</v>
       </c>
       <c r="I52" t="n">
-        <v>872.04</v>
+        <v>886.84</v>
       </c>
       <c r="J52" t="n">
-        <v>877.88</v>
+        <v>883.8200000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>868.36</v>
+        <v>907.8200000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>876.6740000000001</v>
+        <v>881.9299999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>9.495798110961914</v>
+        <v>7.844008445739746</v>
       </c>
       <c r="C2" t="n">
-        <v>9.716798782348633</v>
+        <v>7.498397350311279</v>
       </c>
       <c r="D2" t="n">
-        <v>8.450524806976318</v>
+        <v>9.359642267227173</v>
       </c>
       <c r="E2" t="n">
-        <v>8.380640745162964</v>
+        <v>8.748693227767944</v>
       </c>
       <c r="F2" t="n">
-        <v>8.179219245910645</v>
+        <v>8.383124589920044</v>
       </c>
       <c r="G2" t="n">
-        <v>9.429013013839722</v>
+        <v>7.756237745285034</v>
       </c>
       <c r="H2" t="n">
-        <v>9.570173025131226</v>
+        <v>7.474930047988892</v>
       </c>
       <c r="I2" t="n">
-        <v>9.474365234375</v>
+        <v>8.923778533935547</v>
       </c>
       <c r="J2" t="n">
-        <v>9.108386993408203</v>
+        <v>8.989065885543823</v>
       </c>
       <c r="K2" t="n">
-        <v>7.684460639953613</v>
+        <v>9.777573585510254</v>
       </c>
       <c r="L2" t="n">
-        <v>8.948938059806824</v>
+        <v>8.475545167922974</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>9.178146839141846</v>
+        <v>7.378678560256958</v>
       </c>
       <c r="C3" t="n">
-        <v>7.876542091369629</v>
+        <v>8.609622955322266</v>
       </c>
       <c r="D3" t="n">
-        <v>8.201158285140991</v>
+        <v>8.919745445251465</v>
       </c>
       <c r="E3" t="n">
-        <v>9.348717927932739</v>
+        <v>8.763162136077881</v>
       </c>
       <c r="F3" t="n">
-        <v>10.12971186637878</v>
+        <v>8.952173948287964</v>
       </c>
       <c r="G3" t="n">
-        <v>8.561753511428833</v>
+        <v>7.49141788482666</v>
       </c>
       <c r="H3" t="n">
-        <v>9.088523864746094</v>
+        <v>8.849101781845093</v>
       </c>
       <c r="I3" t="n">
-        <v>8.634983777999878</v>
+        <v>7.75573468208313</v>
       </c>
       <c r="J3" t="n">
-        <v>8.343278169631958</v>
+        <v>9.183677434921265</v>
       </c>
       <c r="K3" t="n">
-        <v>9.254946231842041</v>
+        <v>8.439581871032715</v>
       </c>
       <c r="L3" t="n">
-        <v>8.86177625656128</v>
+        <v>8.434289669990539</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>8.344253063201904</v>
+        <v>9.197568655014038</v>
       </c>
       <c r="C4" t="n">
-        <v>8.889897108078003</v>
+        <v>7.791179895401001</v>
       </c>
       <c r="D4" t="n">
-        <v>9.070198774337769</v>
+        <v>8.791107892990112</v>
       </c>
       <c r="E4" t="n">
-        <v>8.984652996063232</v>
+        <v>8.798582553863525</v>
       </c>
       <c r="F4" t="n">
-        <v>9.841452598571777</v>
+        <v>7.546798229217529</v>
       </c>
       <c r="G4" t="n">
-        <v>9.209120512008667</v>
+        <v>9.256385564804077</v>
       </c>
       <c r="H4" t="n">
-        <v>9.5980544090271</v>
+        <v>8.626065015792847</v>
       </c>
       <c r="I4" t="n">
-        <v>9.560662269592285</v>
+        <v>7.923311471939087</v>
       </c>
       <c r="J4" t="n">
-        <v>9.544694185256958</v>
+        <v>7.986642599105835</v>
       </c>
       <c r="K4" t="n">
-        <v>7.577274322509766</v>
+        <v>9.528218030929565</v>
       </c>
       <c r="L4" t="n">
-        <v>9.062026023864746</v>
+        <v>8.544585990905762</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.206269264221191</v>
+        <v>7.371720790863037</v>
       </c>
       <c r="C5" t="n">
-        <v>7.711407899856567</v>
+        <v>7.55776047706604</v>
       </c>
       <c r="D5" t="n">
-        <v>7.806699275970459</v>
+        <v>8.252105712890625</v>
       </c>
       <c r="E5" t="n">
-        <v>7.220176935195923</v>
+        <v>6.829582691192627</v>
       </c>
       <c r="F5" t="n">
-        <v>7.400722742080688</v>
+        <v>7.687897920608521</v>
       </c>
       <c r="G5" t="n">
-        <v>7.196751356124878</v>
+        <v>7.969209909439087</v>
       </c>
       <c r="H5" t="n">
-        <v>8.342260837554932</v>
+        <v>8.100878477096558</v>
       </c>
       <c r="I5" t="n">
-        <v>8.483884811401367</v>
+        <v>7.90436315536499</v>
       </c>
       <c r="J5" t="n">
-        <v>7.37278151512146</v>
+        <v>7.326873540878296</v>
       </c>
       <c r="K5" t="n">
-        <v>8.329810380935669</v>
+        <v>8.014556407928467</v>
       </c>
       <c r="L5" t="n">
-        <v>7.707076501846314</v>
+        <v>7.701494908332824</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.691788196563721</v>
+        <v>8.093863725662231</v>
       </c>
       <c r="C6" t="n">
-        <v>7.328409194946289</v>
+        <v>8.67340874671936</v>
       </c>
       <c r="D6" t="n">
-        <v>8.539262533187866</v>
+        <v>7.82405686378479</v>
       </c>
       <c r="E6" t="n">
-        <v>7.512941360473633</v>
+        <v>7.574682474136353</v>
       </c>
       <c r="F6" t="n">
-        <v>8.62853217124939</v>
+        <v>7.499989748001099</v>
       </c>
       <c r="G6" t="n">
-        <v>8.185706853866577</v>
+        <v>7.613207578659058</v>
       </c>
       <c r="H6" t="n">
-        <v>7.752302408218384</v>
+        <v>7.092019557952881</v>
       </c>
       <c r="I6" t="n">
-        <v>7.846067905426025</v>
+        <v>7.457590579986572</v>
       </c>
       <c r="J6" t="n">
-        <v>7.894418478012085</v>
+        <v>7.895930767059326</v>
       </c>
       <c r="K6" t="n">
-        <v>8.282977819442749</v>
+        <v>7.612185478210449</v>
       </c>
       <c r="L6" t="n">
-        <v>7.966240692138672</v>
+        <v>7.733693552017212</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>9.63417911529541</v>
+        <v>8.591621160507202</v>
       </c>
       <c r="C7" t="n">
-        <v>8.557174444198608</v>
+        <v>8.859935283660889</v>
       </c>
       <c r="D7" t="n">
-        <v>7.972220182418823</v>
+        <v>7.819639205932617</v>
       </c>
       <c r="E7" t="n">
-        <v>7.77914571762085</v>
+        <v>8.71581506729126</v>
       </c>
       <c r="F7" t="n">
-        <v>8.487647533416748</v>
+        <v>8.447513341903687</v>
       </c>
       <c r="G7" t="n">
-        <v>8.438054800033569</v>
+        <v>8.448978662490845</v>
       </c>
       <c r="H7" t="n">
-        <v>7.685964345932007</v>
+        <v>8.248503684997559</v>
       </c>
       <c r="I7" t="n">
-        <v>8.349285840988159</v>
+        <v>8.423069715499878</v>
       </c>
       <c r="J7" t="n">
-        <v>9.264846086502075</v>
+        <v>9.100831270217896</v>
       </c>
       <c r="K7" t="n">
-        <v>8.526283979415894</v>
+        <v>8.211613178253174</v>
       </c>
       <c r="L7" t="n">
-        <v>8.469480204582215</v>
+        <v>8.486752057075501</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>7.719922780990601</v>
+        <v>9.242972373962402</v>
       </c>
       <c r="C8" t="n">
-        <v>7.83004355430603</v>
+        <v>8.764558792114258</v>
       </c>
       <c r="D8" t="n">
-        <v>8.419554710388184</v>
+        <v>7.952244281768799</v>
       </c>
       <c r="E8" t="n">
-        <v>7.665940046310425</v>
+        <v>8.081721544265747</v>
       </c>
       <c r="F8" t="n">
-        <v>8.77013897895813</v>
+        <v>8.609599828720093</v>
       </c>
       <c r="G8" t="n">
-        <v>8.380613565444946</v>
+        <v>8.030101299285889</v>
       </c>
       <c r="H8" t="n">
-        <v>7.934284448623657</v>
+        <v>8.247518062591553</v>
       </c>
       <c r="I8" t="n">
-        <v>7.795138597488403</v>
+        <v>8.070531606674194</v>
       </c>
       <c r="J8" t="n">
-        <v>8.12577486038208</v>
+        <v>8.443028450012207</v>
       </c>
       <c r="K8" t="n">
-        <v>8.878875017166138</v>
+        <v>8.573174238204956</v>
       </c>
       <c r="L8" t="n">
-        <v>8.152028656005859</v>
+        <v>8.40154504776001</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.324266672134399</v>
+        <v>7.485004425048828</v>
       </c>
       <c r="C9" t="n">
-        <v>7.722368001937866</v>
+        <v>7.830255746841431</v>
       </c>
       <c r="D9" t="n">
-        <v>7.515335559844971</v>
+        <v>7.843980073928833</v>
       </c>
       <c r="E9" t="n">
-        <v>7.653478145599365</v>
+        <v>7.826538562774658</v>
       </c>
       <c r="F9" t="n">
-        <v>9.424038171768188</v>
+        <v>8.772139072418213</v>
       </c>
       <c r="G9" t="n">
-        <v>7.533313512802124</v>
+        <v>8.413644552230835</v>
       </c>
       <c r="H9" t="n">
-        <v>9.644938707351685</v>
+        <v>7.654473543167114</v>
       </c>
       <c r="I9" t="n">
-        <v>9.554113864898682</v>
+        <v>8.559181928634644</v>
       </c>
       <c r="J9" t="n">
-        <v>7.532275199890137</v>
+        <v>7.629538059234619</v>
       </c>
       <c r="K9" t="n">
-        <v>8.166176080703735</v>
+        <v>9.425014972686768</v>
       </c>
       <c r="L9" t="n">
-        <v>8.307030391693115</v>
+        <v>8.143977093696595</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>9.000535249710083</v>
+        <v>7.057509422302246</v>
       </c>
       <c r="C10" t="n">
-        <v>7.381162881851196</v>
+        <v>7.681402683258057</v>
       </c>
       <c r="D10" t="n">
-        <v>7.194674968719482</v>
+        <v>7.303900480270386</v>
       </c>
       <c r="E10" t="n">
-        <v>8.373211145401001</v>
+        <v>6.688457250595093</v>
       </c>
       <c r="F10" t="n">
-        <v>7.29489278793335</v>
+        <v>6.944800138473511</v>
       </c>
       <c r="G10" t="n">
-        <v>7.334764003753662</v>
+        <v>7.240547180175781</v>
       </c>
       <c r="H10" t="n">
-        <v>7.740749835968018</v>
+        <v>6.942322492599487</v>
       </c>
       <c r="I10" t="n">
-        <v>9.343168973922729</v>
+        <v>7.030075073242188</v>
       </c>
       <c r="J10" t="n">
-        <v>7.328833818435669</v>
+        <v>7.41208028793335</v>
       </c>
       <c r="K10" t="n">
-        <v>7.791122436523438</v>
+        <v>8.31068229675293</v>
       </c>
       <c r="L10" t="n">
-        <v>7.878311610221862</v>
+        <v>7.261177730560303</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.622537136077881</v>
+        <v>8.989159107208252</v>
       </c>
       <c r="C11" t="n">
-        <v>7.268478155136108</v>
+        <v>7.705268383026123</v>
       </c>
       <c r="D11" t="n">
-        <v>8.358758687973022</v>
+        <v>6.842082738876343</v>
       </c>
       <c r="E11" t="n">
-        <v>6.692904949188232</v>
+        <v>7.010145902633667</v>
       </c>
       <c r="F11" t="n">
-        <v>6.937304019927979</v>
+        <v>7.011600732803345</v>
       </c>
       <c r="G11" t="n">
-        <v>6.869506597518921</v>
+        <v>6.95575737953186</v>
       </c>
       <c r="H11" t="n">
-        <v>6.872981548309326</v>
+        <v>6.640066385269165</v>
       </c>
       <c r="I11" t="n">
-        <v>7.091890096664429</v>
+        <v>6.859013795852661</v>
       </c>
       <c r="J11" t="n">
-        <v>6.994170665740967</v>
+        <v>8.388123989105225</v>
       </c>
       <c r="K11" t="n">
-        <v>7.497402667999268</v>
+        <v>7.090435743331909</v>
       </c>
       <c r="L11" t="n">
-        <v>7.220593452453613</v>
+        <v>7.349165415763855</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.954201698303223</v>
+        <v>7.596640110015869</v>
       </c>
       <c r="C12" t="n">
-        <v>7.530781507492065</v>
+        <v>7.810075521469116</v>
       </c>
       <c r="D12" t="n">
-        <v>7.775675296783447</v>
+        <v>8.759162425994873</v>
       </c>
       <c r="E12" t="n">
-        <v>8.524754285812378</v>
+        <v>7.635072708129883</v>
       </c>
       <c r="F12" t="n">
-        <v>8.246986865997314</v>
+        <v>7.690389156341553</v>
       </c>
       <c r="G12" t="n">
-        <v>7.814074993133545</v>
+        <v>6.970366716384888</v>
       </c>
       <c r="H12" t="n">
-        <v>7.711859226226807</v>
+        <v>7.947258710861206</v>
       </c>
       <c r="I12" t="n">
-        <v>8.947083711624146</v>
+        <v>7.558760166168213</v>
       </c>
       <c r="J12" t="n">
-        <v>7.670929193496704</v>
+        <v>8.248984336853027</v>
       </c>
       <c r="K12" t="n">
-        <v>7.94323468208313</v>
+        <v>7.723804235458374</v>
       </c>
       <c r="L12" t="n">
-        <v>8.011958146095276</v>
+        <v>7.7940514087677</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>8.293347597122192</v>
+        <v>6.843070983886719</v>
       </c>
       <c r="C13" t="n">
-        <v>8.285855054855347</v>
+        <v>7.271481275558472</v>
       </c>
       <c r="D13" t="n">
-        <v>8.80852198600769</v>
+        <v>9.623519420623779</v>
       </c>
       <c r="E13" t="n">
-        <v>8.480850458145142</v>
+        <v>7.084501028060913</v>
       </c>
       <c r="F13" t="n">
-        <v>7.424094915390015</v>
+        <v>6.909891366958618</v>
       </c>
       <c r="G13" t="n">
-        <v>8.744094371795654</v>
+        <v>7.76067852973938</v>
       </c>
       <c r="H13" t="n">
-        <v>8.102384567260742</v>
+        <v>8.131751775741577</v>
       </c>
       <c r="I13" t="n">
-        <v>7.256102085113525</v>
+        <v>8.355738639831543</v>
       </c>
       <c r="J13" t="n">
-        <v>6.96686053276062</v>
+        <v>8.237015008926392</v>
       </c>
       <c r="K13" t="n">
-        <v>8.023127555847168</v>
+        <v>6.906947135925293</v>
       </c>
       <c r="L13" t="n">
-        <v>8.03852391242981</v>
+        <v>7.712459516525269</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.622144222259521</v>
+        <v>8.491871356964111</v>
       </c>
       <c r="C14" t="n">
-        <v>8.711819648742676</v>
+        <v>8.485363006591797</v>
       </c>
       <c r="D14" t="n">
-        <v>8.574689388275146</v>
+        <v>8.23998498916626</v>
       </c>
       <c r="E14" t="n">
-        <v>8.59665584564209</v>
+        <v>8.040999412536621</v>
       </c>
       <c r="F14" t="n">
-        <v>9.151654958724976</v>
+        <v>8.187658309936523</v>
       </c>
       <c r="G14" t="n">
-        <v>8.239519596099854</v>
+        <v>10.03341555595398</v>
       </c>
       <c r="H14" t="n">
-        <v>8.521330595016479</v>
+        <v>8.748697996139526</v>
       </c>
       <c r="I14" t="n">
-        <v>8.227582931518555</v>
+        <v>7.69038724899292</v>
       </c>
       <c r="J14" t="n">
-        <v>7.821682691574097</v>
+        <v>8.920262575149536</v>
       </c>
       <c r="K14" t="n">
-        <v>9.652911901473999</v>
+        <v>8.541250705718994</v>
       </c>
       <c r="L14" t="n">
-        <v>8.51199917793274</v>
+        <v>8.537989115715027</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>8.823029279708862</v>
+        <v>8.383637428283691</v>
       </c>
       <c r="C15" t="n">
-        <v>8.962157011032104</v>
+        <v>8.009135007858276</v>
       </c>
       <c r="D15" t="n">
-        <v>9.570079565048218</v>
+        <v>9.392076253890991</v>
       </c>
       <c r="E15" t="n">
-        <v>8.418090343475342</v>
+        <v>8.129168748855591</v>
       </c>
       <c r="F15" t="n">
-        <v>9.345166921615601</v>
+        <v>9.181528568267822</v>
       </c>
       <c r="G15" t="n">
-        <v>9.025498151779175</v>
+        <v>9.406568765640259</v>
       </c>
       <c r="H15" t="n">
-        <v>10.40110230445862</v>
+        <v>8.696364164352417</v>
       </c>
       <c r="I15" t="n">
-        <v>10.19249558448792</v>
+        <v>8.603746175765991</v>
       </c>
       <c r="J15" t="n">
-        <v>9.567585468292236</v>
+        <v>8.301365852355957</v>
       </c>
       <c r="K15" t="n">
-        <v>10.14460706710815</v>
+        <v>9.345691442489624</v>
       </c>
       <c r="L15" t="n">
-        <v>9.444981169700622</v>
+        <v>8.744928240776062</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>9.096326589584351</v>
+        <v>9.366592645645142</v>
       </c>
       <c r="C16" t="n">
-        <v>8.105844497680664</v>
+        <v>7.14377236366272</v>
       </c>
       <c r="D16" t="n">
-        <v>7.724817514419556</v>
+        <v>9.423998594284058</v>
       </c>
       <c r="E16" t="n">
-        <v>7.729805707931519</v>
+        <v>8.806057691574097</v>
       </c>
       <c r="F16" t="n">
-        <v>7.764675855636597</v>
+        <v>7.150793075561523</v>
       </c>
       <c r="G16" t="n">
-        <v>7.290896892547607</v>
+        <v>7.667434215545654</v>
       </c>
       <c r="H16" t="n">
-        <v>7.704835414886475</v>
+        <v>7.74832010269165</v>
       </c>
       <c r="I16" t="n">
-        <v>7.814133167266846</v>
+        <v>7.680407047271729</v>
       </c>
       <c r="J16" t="n">
-        <v>9.021419286727905</v>
+        <v>7.40213680267334</v>
       </c>
       <c r="K16" t="n">
-        <v>7.883569955825806</v>
+        <v>7.659461259841919</v>
       </c>
       <c r="L16" t="n">
-        <v>8.013632488250732</v>
+        <v>8.004897379875183</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>8.148791790008545</v>
+        <v>8.239012002944946</v>
       </c>
       <c r="C17" t="n">
-        <v>8.788615465164185</v>
+        <v>8.509506464004517</v>
       </c>
       <c r="D17" t="n">
-        <v>8.276896953582764</v>
+        <v>9.078882455825806</v>
       </c>
       <c r="E17" t="n">
-        <v>8.198858261108398</v>
+        <v>8.348780870437622</v>
       </c>
       <c r="F17" t="n">
-        <v>8.073912858963013</v>
+        <v>8.857426404953003</v>
       </c>
       <c r="G17" t="n">
-        <v>8.110325813293457</v>
+        <v>8.051466226577759</v>
       </c>
       <c r="H17" t="n">
-        <v>8.383644104003906</v>
+        <v>10.2942898273468</v>
       </c>
       <c r="I17" t="n">
-        <v>8.308385848999023</v>
+        <v>7.886434555053711</v>
       </c>
       <c r="J17" t="n">
-        <v>7.928282022476196</v>
+        <v>8.056480646133423</v>
       </c>
       <c r="K17" t="n">
-        <v>7.342788457870483</v>
+        <v>9.099291563034058</v>
       </c>
       <c r="L17" t="n">
-        <v>8.156050157546996</v>
+        <v>8.642157101631165</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>9.505262851715088</v>
+        <v>8.769654750823975</v>
       </c>
       <c r="C18" t="n">
-        <v>9.047941446304321</v>
+        <v>8.758169889450073</v>
       </c>
       <c r="D18" t="n">
-        <v>9.296293020248413</v>
+        <v>9.565078020095825</v>
       </c>
       <c r="E18" t="n">
-        <v>10.08878564834595</v>
+        <v>8.69239354133606</v>
       </c>
       <c r="F18" t="n">
-        <v>10.09724164009094</v>
+        <v>9.24650502204895</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4678795337677</v>
+        <v>8.631054878234863</v>
       </c>
       <c r="H18" t="n">
-        <v>9.008015155792236</v>
+        <v>9.901224613189697</v>
       </c>
       <c r="I18" t="n">
-        <v>8.779104709625244</v>
+        <v>10.18550062179565</v>
       </c>
       <c r="J18" t="n">
-        <v>9.508257389068604</v>
+        <v>8.626522541046143</v>
       </c>
       <c r="K18" t="n">
-        <v>9.271865606307983</v>
+        <v>9.340222835540771</v>
       </c>
       <c r="L18" t="n">
-        <v>9.307064700126649</v>
+        <v>9.171632671356202</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.711041450500488</v>
+        <v>7.013757228851318</v>
       </c>
       <c r="C19" t="n">
-        <v>8.203124523162842</v>
+        <v>6.672114372253418</v>
       </c>
       <c r="D19" t="n">
-        <v>7.29351019859314</v>
+        <v>8.962141990661621</v>
       </c>
       <c r="E19" t="n">
-        <v>6.602808713912964</v>
+        <v>6.749943971633911</v>
       </c>
       <c r="F19" t="n">
-        <v>6.174928903579712</v>
+        <v>6.917481422424316</v>
       </c>
       <c r="G19" t="n">
-        <v>6.870097160339355</v>
+        <v>7.099007129669189</v>
       </c>
       <c r="H19" t="n">
-        <v>7.072094678878784</v>
+        <v>6.95589804649353</v>
       </c>
       <c r="I19" t="n">
-        <v>6.704024314880371</v>
+        <v>7.879496335983276</v>
       </c>
       <c r="J19" t="n">
-        <v>7.500514984130859</v>
+        <v>7.046072244644165</v>
       </c>
       <c r="K19" t="n">
-        <v>6.695083141326904</v>
+        <v>7.913337469100952</v>
       </c>
       <c r="L19" t="n">
-        <v>6.982722806930542</v>
+        <v>7.32092502117157</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.456069231033325</v>
+        <v>8.426502704620361</v>
       </c>
       <c r="C20" t="n">
-        <v>7.383267164230347</v>
+        <v>6.930869579315186</v>
       </c>
       <c r="D20" t="n">
-        <v>9.035986423492432</v>
+        <v>8.41253662109375</v>
       </c>
       <c r="E20" t="n">
-        <v>8.344843149185181</v>
+        <v>7.428046226501465</v>
       </c>
       <c r="F20" t="n">
-        <v>7.704484701156616</v>
+        <v>8.529749870300293</v>
       </c>
       <c r="G20" t="n">
-        <v>8.506362676620483</v>
+        <v>7.718800783157349</v>
       </c>
       <c r="H20" t="n">
-        <v>8.051051139831543</v>
+        <v>8.096916198730469</v>
       </c>
       <c r="I20" t="n">
-        <v>7.623545408248901</v>
+        <v>9.232486009597778</v>
       </c>
       <c r="J20" t="n">
-        <v>9.303795099258423</v>
+        <v>7.622418642044067</v>
       </c>
       <c r="K20" t="n">
-        <v>7.89669132232666</v>
+        <v>10.09027314186096</v>
       </c>
       <c r="L20" t="n">
-        <v>8.130609631538391</v>
+        <v>8.248859977722168</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>8.130372285842896</v>
+        <v>8.548254251480103</v>
       </c>
       <c r="C21" t="n">
-        <v>7.822640657424927</v>
+        <v>8.133320808410645</v>
       </c>
       <c r="D21" t="n">
-        <v>7.928854465484619</v>
+        <v>7.884955883026123</v>
       </c>
       <c r="E21" t="n">
-        <v>7.854047775268555</v>
+        <v>9.064410448074341</v>
       </c>
       <c r="F21" t="n">
-        <v>7.927825927734375</v>
+        <v>9.153197765350342</v>
       </c>
       <c r="G21" t="n">
-        <v>8.293394804000854</v>
+        <v>8.281433343887329</v>
       </c>
       <c r="H21" t="n">
-        <v>9.536666631698608</v>
+        <v>7.993184566497803</v>
       </c>
       <c r="I21" t="n">
-        <v>8.998603343963623</v>
+        <v>8.692901372909546</v>
       </c>
       <c r="J21" t="n">
-        <v>8.96864914894104</v>
+        <v>7.701485633850098</v>
       </c>
       <c r="K21" t="n">
-        <v>8.549226999282837</v>
+        <v>8.959179401397705</v>
       </c>
       <c r="L21" t="n">
-        <v>8.401028203964234</v>
+        <v>8.441232347488404</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>7.353374481201172</v>
+        <v>9.10167932510376</v>
       </c>
       <c r="C22" t="n">
-        <v>7.857049465179443</v>
+        <v>8.188668489456177</v>
       </c>
       <c r="D22" t="n">
-        <v>8.642525672912598</v>
+        <v>7.370290994644165</v>
       </c>
       <c r="E22" t="n">
-        <v>8.309868335723877</v>
+        <v>7.841573476791382</v>
       </c>
       <c r="F22" t="n">
-        <v>8.014127492904663</v>
+        <v>8.423573970794678</v>
       </c>
       <c r="G22" t="n">
-        <v>8.138279438018799</v>
+        <v>7.305976629257202</v>
       </c>
       <c r="H22" t="n">
-        <v>7.671544075012207</v>
+        <v>8.414107322692871</v>
       </c>
       <c r="I22" t="n">
-        <v>8.438050985336304</v>
+        <v>7.530393362045288</v>
       </c>
       <c r="J22" t="n">
-        <v>7.323439121246338</v>
+        <v>7.942844152450562</v>
       </c>
       <c r="K22" t="n">
-        <v>9.409478664398193</v>
+        <v>8.712810516357422</v>
       </c>
       <c r="L22" t="n">
-        <v>8.115773773193359</v>
+        <v>8.08319182395935</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.340798139572144</v>
+        <v>10.87584900856018</v>
       </c>
       <c r="C23" t="n">
-        <v>10.60141396522522</v>
+        <v>8.514842987060547</v>
       </c>
       <c r="D23" t="n">
-        <v>10.28431081771851</v>
+        <v>9.554734706878662</v>
       </c>
       <c r="E23" t="n">
-        <v>9.110268592834473</v>
+        <v>8.426030397415161</v>
       </c>
       <c r="F23" t="n">
-        <v>10.0763304233551</v>
+        <v>10.34122633934021</v>
       </c>
       <c r="G23" t="n">
-        <v>9.944107532501221</v>
+        <v>8.572634220123291</v>
       </c>
       <c r="H23" t="n">
-        <v>9.182620525360107</v>
+        <v>8.331268548965454</v>
       </c>
       <c r="I23" t="n">
-        <v>8.348228216171265</v>
+        <v>8.294844627380371</v>
       </c>
       <c r="J23" t="n">
-        <v>9.664839029312134</v>
+        <v>9.344183921813965</v>
       </c>
       <c r="K23" t="n">
-        <v>9.046917200088501</v>
+        <v>9.311777114868164</v>
       </c>
       <c r="L23" t="n">
-        <v>9.459983444213867</v>
+        <v>9.1567391872406</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.405137777328491</v>
+        <v>8.542733669281006</v>
       </c>
       <c r="C24" t="n">
-        <v>8.356210947036743</v>
+        <v>8.248007774353027</v>
       </c>
       <c r="D24" t="n">
-        <v>6.830188035964966</v>
+        <v>7.464483737945557</v>
       </c>
       <c r="E24" t="n">
-        <v>7.24602222442627</v>
+        <v>8.174642562866211</v>
       </c>
       <c r="F24" t="n">
-        <v>8.532742500305176</v>
+        <v>8.045502185821533</v>
       </c>
       <c r="G24" t="n">
-        <v>7.20265007019043</v>
+        <v>8.377662181854248</v>
       </c>
       <c r="H24" t="n">
-        <v>8.638972282409668</v>
+        <v>7.693024158477783</v>
       </c>
       <c r="I24" t="n">
-        <v>7.097405195236206</v>
+        <v>7.989181041717529</v>
       </c>
       <c r="J24" t="n">
-        <v>7.335802793502808</v>
+        <v>7.267116546630859</v>
       </c>
       <c r="K24" t="n">
-        <v>8.336259603500366</v>
+        <v>8.519336700439453</v>
       </c>
       <c r="L24" t="n">
-        <v>7.698139142990112</v>
+        <v>8.03216905593872</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>9.479329824447632</v>
+        <v>9.157196521759033</v>
       </c>
       <c r="C25" t="n">
-        <v>9.421008348464966</v>
+        <v>8.570207595825195</v>
       </c>
       <c r="D25" t="n">
-        <v>12.66970372200012</v>
+        <v>10.55827236175537</v>
       </c>
       <c r="E25" t="n">
-        <v>9.733669519424438</v>
+        <v>9.892277717590332</v>
       </c>
       <c r="F25" t="n">
-        <v>8.873887777328491</v>
+        <v>9.816989898681641</v>
       </c>
       <c r="G25" t="n">
-        <v>10.06738257408142</v>
+        <v>9.068821668624878</v>
       </c>
       <c r="H25" t="n">
-        <v>10.11273288726807</v>
+        <v>9.292814016342163</v>
       </c>
       <c r="I25" t="n">
-        <v>8.416543960571289</v>
+        <v>10.56485033035278</v>
       </c>
       <c r="J25" t="n">
-        <v>10.42941761016846</v>
+        <v>9.093818664550781</v>
       </c>
       <c r="K25" t="n">
-        <v>8.804040908813477</v>
+        <v>10.74961042404175</v>
       </c>
       <c r="L25" t="n">
-        <v>9.800771713256836</v>
+        <v>9.676485919952393</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.434470415115356</v>
+        <v>8.732238531112671</v>
       </c>
       <c r="C26" t="n">
-        <v>9.826953172683716</v>
+        <v>9.339699506759644</v>
       </c>
       <c r="D26" t="n">
-        <v>8.892817497253418</v>
+        <v>9.783071041107178</v>
       </c>
       <c r="E26" t="n">
-        <v>8.182626962661743</v>
+        <v>8.231008529663086</v>
       </c>
       <c r="F26" t="n">
-        <v>8.388602256774902</v>
+        <v>7.808091640472412</v>
       </c>
       <c r="G26" t="n">
-        <v>8.167189836502075</v>
+        <v>9.123248100280762</v>
       </c>
       <c r="H26" t="n">
-        <v>8.808549642562866</v>
+        <v>9.634442806243896</v>
       </c>
       <c r="I26" t="n">
-        <v>9.153143405914307</v>
+        <v>8.464415550231934</v>
       </c>
       <c r="J26" t="n">
-        <v>9.242462873458862</v>
+        <v>9.235071182250977</v>
       </c>
       <c r="K26" t="n">
-        <v>8.993053674697876</v>
+        <v>9.824479341506958</v>
       </c>
       <c r="L26" t="n">
-        <v>8.808986973762511</v>
+        <v>9.017576622962952</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>8.9048011302948</v>
+        <v>9.008572578430176</v>
       </c>
       <c r="C27" t="n">
-        <v>9.687416315078735</v>
+        <v>8.952535152435303</v>
       </c>
       <c r="D27" t="n">
-        <v>9.332705020904541</v>
+        <v>10.57605457305908</v>
       </c>
       <c r="E27" t="n">
-        <v>10.04288220405579</v>
+        <v>9.271420955657959</v>
       </c>
       <c r="F27" t="n">
-        <v>10.9834942817688</v>
+        <v>9.303829908370972</v>
       </c>
       <c r="G27" t="n">
-        <v>8.639345407485962</v>
+        <v>9.92320704460144</v>
       </c>
       <c r="H27" t="n">
-        <v>8.88982629776001</v>
+        <v>10.01246690750122</v>
       </c>
       <c r="I27" t="n">
-        <v>9.542197227478027</v>
+        <v>9.697826623916626</v>
       </c>
       <c r="J27" t="n">
-        <v>9.640565633773804</v>
+        <v>10.23592448234558</v>
       </c>
       <c r="K27" t="n">
-        <v>10.85182642936707</v>
+        <v>9.312744855880737</v>
       </c>
       <c r="L27" t="n">
-        <v>9.651505994796754</v>
+        <v>9.62945830821991</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.526305913925171</v>
+        <v>8.888323545455933</v>
       </c>
       <c r="C28" t="n">
-        <v>8.319315195083618</v>
+        <v>7.370220422744751</v>
       </c>
       <c r="D28" t="n">
-        <v>7.419083595275879</v>
+        <v>7.35979175567627</v>
       </c>
       <c r="E28" t="n">
-        <v>8.846548318862915</v>
+        <v>8.370686292648315</v>
       </c>
       <c r="F28" t="n">
-        <v>7.495397806167603</v>
+        <v>7.496382713317871</v>
       </c>
       <c r="G28" t="n">
-        <v>8.109946012496948</v>
+        <v>7.426063060760498</v>
       </c>
       <c r="H28" t="n">
-        <v>8.137326240539551</v>
+        <v>7.107364177703857</v>
       </c>
       <c r="I28" t="n">
-        <v>7.594255924224854</v>
+        <v>8.13375997543335</v>
       </c>
       <c r="J28" t="n">
-        <v>7.002775192260742</v>
+        <v>8.003606557846069</v>
       </c>
       <c r="K28" t="n">
-        <v>7.602703094482422</v>
+        <v>8.416579246520996</v>
       </c>
       <c r="L28" t="n">
-        <v>7.80536572933197</v>
+        <v>7.857277774810791</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>8.140292644500732</v>
+        <v>7.673422336578369</v>
       </c>
       <c r="C29" t="n">
-        <v>7.817631006240845</v>
+        <v>7.477430820465088</v>
       </c>
       <c r="D29" t="n">
-        <v>7.283589839935303</v>
+        <v>8.332279205322266</v>
       </c>
       <c r="E29" t="n">
-        <v>7.570775032043457</v>
+        <v>7.729822397232056</v>
       </c>
       <c r="F29" t="n">
-        <v>7.571271657943726</v>
+        <v>7.901339769363403</v>
       </c>
       <c r="G29" t="n">
-        <v>7.782266139984131</v>
+        <v>7.77847695350647</v>
       </c>
       <c r="H29" t="n">
-        <v>8.184852361679077</v>
+        <v>8.336796760559082</v>
       </c>
       <c r="I29" t="n">
-        <v>7.91532826423645</v>
+        <v>7.994195222854614</v>
       </c>
       <c r="J29" t="n">
-        <v>8.430504560470581</v>
+        <v>7.536862134933472</v>
       </c>
       <c r="K29" t="n">
-        <v>8.079889297485352</v>
+        <v>8.074974298477173</v>
       </c>
       <c r="L29" t="n">
-        <v>7.877640080451966</v>
+        <v>7.883559989929199</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.30188512802124</v>
+        <v>7.410687923431396</v>
       </c>
       <c r="C30" t="n">
-        <v>8.000120639801025</v>
+        <v>7.240152597427368</v>
       </c>
       <c r="D30" t="n">
-        <v>7.23905086517334</v>
+        <v>10.19199013710022</v>
       </c>
       <c r="E30" t="n">
-        <v>7.702641487121582</v>
+        <v>7.597242116928101</v>
       </c>
       <c r="F30" t="n">
-        <v>8.145241975784302</v>
+        <v>7.585229873657227</v>
       </c>
       <c r="G30" t="n">
-        <v>7.776658296585083</v>
+        <v>7.453609466552734</v>
       </c>
       <c r="H30" t="n">
-        <v>7.528332233428955</v>
+        <v>7.338392019271851</v>
       </c>
       <c r="I30" t="n">
-        <v>8.092898368835449</v>
+        <v>7.651077747344971</v>
       </c>
       <c r="J30" t="n">
-        <v>7.639519929885864</v>
+        <v>8.265455007553101</v>
       </c>
       <c r="K30" t="n">
-        <v>7.510364770889282</v>
+        <v>7.901918172836304</v>
       </c>
       <c r="L30" t="n">
-        <v>7.693671369552613</v>
+        <v>7.863575506210327</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.491920948028564</v>
+        <v>8.084439277648926</v>
       </c>
       <c r="C31" t="n">
-        <v>9.363136291503906</v>
+        <v>8.145328521728516</v>
       </c>
       <c r="D31" t="n">
-        <v>9.798486232757568</v>
+        <v>7.975237131118774</v>
       </c>
       <c r="E31" t="n">
-        <v>8.72722339630127</v>
+        <v>9.303329467773438</v>
       </c>
       <c r="F31" t="n">
-        <v>8.748686075210571</v>
+        <v>7.393245220184326</v>
       </c>
       <c r="G31" t="n">
-        <v>9.387547731399536</v>
+        <v>7.696982383728027</v>
       </c>
       <c r="H31" t="n">
-        <v>8.380620956420898</v>
+        <v>8.198079347610474</v>
       </c>
       <c r="I31" t="n">
-        <v>8.584600925445557</v>
+        <v>9.276959419250488</v>
       </c>
       <c r="J31" t="n">
-        <v>9.422973394393921</v>
+        <v>8.533902406692505</v>
       </c>
       <c r="K31" t="n">
-        <v>8.763671159744263</v>
+        <v>9.484802007675171</v>
       </c>
       <c r="L31" t="n">
-        <v>8.966886711120605</v>
+        <v>8.409230518341065</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>8.098891258239746</v>
+        <v>8.375138521194458</v>
       </c>
       <c r="C32" t="n">
-        <v>9.054885387420654</v>
+        <v>9.069377183914185</v>
       </c>
       <c r="D32" t="n">
-        <v>8.958178997039795</v>
+        <v>8.412570238113403</v>
       </c>
       <c r="E32" t="n">
-        <v>9.51323127746582</v>
+        <v>9.582051992416382</v>
       </c>
       <c r="F32" t="n">
-        <v>8.435502529144287</v>
+        <v>11.19568991661072</v>
       </c>
       <c r="G32" t="n">
-        <v>9.620494604110718</v>
+        <v>9.586741209030151</v>
       </c>
       <c r="H32" t="n">
-        <v>8.588566780090332</v>
+        <v>9.704779148101807</v>
       </c>
       <c r="I32" t="n">
-        <v>10.10572648048401</v>
+        <v>10.49574685096741</v>
       </c>
       <c r="J32" t="n">
-        <v>10.769526720047</v>
+        <v>9.463866233825684</v>
       </c>
       <c r="K32" t="n">
-        <v>8.307811260223389</v>
+        <v>9.594634532928467</v>
       </c>
       <c r="L32" t="n">
-        <v>9.145281529426574</v>
+        <v>9.548059582710266</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.808063983917236</v>
+        <v>9.910960674285889</v>
       </c>
       <c r="C33" t="n">
-        <v>9.054985046386719</v>
+        <v>8.698853015899658</v>
       </c>
       <c r="D33" t="n">
-        <v>7.671959638595581</v>
+        <v>7.823652505874634</v>
       </c>
       <c r="E33" t="n">
-        <v>8.240981101989746</v>
+        <v>9.00856614112854</v>
       </c>
       <c r="F33" t="n">
-        <v>8.066420078277588</v>
+        <v>8.103428602218628</v>
       </c>
       <c r="G33" t="n">
-        <v>7.706855535507202</v>
+        <v>8.286333799362183</v>
       </c>
       <c r="H33" t="n">
-        <v>7.597641229629517</v>
+        <v>7.687910079956055</v>
       </c>
       <c r="I33" t="n">
-        <v>8.087876558303833</v>
+        <v>7.661500215530396</v>
       </c>
       <c r="J33" t="n">
-        <v>8.842436790466309</v>
+        <v>8.37467098236084</v>
       </c>
       <c r="K33" t="n">
-        <v>8.112824201583862</v>
+        <v>9.979589462280273</v>
       </c>
       <c r="L33" t="n">
-        <v>8.11900441646576</v>
+        <v>8.553546547889709</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>10.66437721252441</v>
+        <v>8.687838315963745</v>
       </c>
       <c r="C34" t="n">
-        <v>10.06290459632874</v>
+        <v>8.347784042358398</v>
       </c>
       <c r="D34" t="n">
-        <v>9.224498510360718</v>
+        <v>10.07149267196655</v>
       </c>
       <c r="E34" t="n">
-        <v>8.292856931686401</v>
+        <v>9.61355996131897</v>
       </c>
       <c r="F34" t="n">
-        <v>9.884280204772949</v>
+        <v>8.876726150512695</v>
       </c>
       <c r="G34" t="n">
-        <v>8.871914625167847</v>
+        <v>9.128738164901733</v>
       </c>
       <c r="H34" t="n">
-        <v>9.860480546951294</v>
+        <v>8.193702220916748</v>
       </c>
       <c r="I34" t="n">
-        <v>9.420982122421265</v>
+        <v>7.865524053573608</v>
       </c>
       <c r="J34" t="n">
-        <v>9.09429407119751</v>
+        <v>8.806065320968628</v>
       </c>
       <c r="K34" t="n">
-        <v>9.244417667388916</v>
+        <v>8.781690359115601</v>
       </c>
       <c r="L34" t="n">
-        <v>9.462100648880005</v>
+        <v>8.837312126159668</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.720805406570435</v>
+        <v>8.212604522705078</v>
       </c>
       <c r="C35" t="n">
-        <v>7.690871715545654</v>
+        <v>8.633540153503418</v>
       </c>
       <c r="D35" t="n">
-        <v>7.989155769348145</v>
+        <v>8.292408227920532</v>
       </c>
       <c r="E35" t="n">
-        <v>8.82049560546875</v>
+        <v>8.356239080429077</v>
       </c>
       <c r="F35" t="n">
-        <v>8.249502420425415</v>
+        <v>8.389697551727295</v>
       </c>
       <c r="G35" t="n">
-        <v>8.318309545516968</v>
+        <v>8.011164665222168</v>
       </c>
       <c r="H35" t="n">
-        <v>8.797155141830444</v>
+        <v>9.151702880859375</v>
       </c>
       <c r="I35" t="n">
-        <v>8.913225650787354</v>
+        <v>8.944743156433105</v>
       </c>
       <c r="J35" t="n">
-        <v>8.293375492095947</v>
+        <v>7.977690935134888</v>
       </c>
       <c r="K35" t="n">
-        <v>9.180588245391846</v>
+        <v>7.757722616195679</v>
       </c>
       <c r="L35" t="n">
-        <v>8.397348499298095</v>
+        <v>8.372751379013062</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>8.671859502792358</v>
+        <v>7.648010015487671</v>
       </c>
       <c r="C36" t="n">
-        <v>7.325798273086548</v>
+        <v>8.407548189163208</v>
       </c>
       <c r="D36" t="n">
-        <v>8.315306186676025</v>
+        <v>7.734786748886108</v>
       </c>
       <c r="E36" t="n">
-        <v>8.660417556762695</v>
+        <v>8.28287410736084</v>
       </c>
       <c r="F36" t="n">
-        <v>9.391546010971069</v>
+        <v>8.461991548538208</v>
       </c>
       <c r="G36" t="n">
-        <v>8.167195558547974</v>
+        <v>8.343786954879761</v>
       </c>
       <c r="H36" t="n">
-        <v>8.00263524055481</v>
+        <v>8.853042602539062</v>
       </c>
       <c r="I36" t="n">
-        <v>7.90333890914917</v>
+        <v>9.270359039306641</v>
       </c>
       <c r="J36" t="n">
-        <v>8.461404323577881</v>
+        <v>8.558214426040649</v>
       </c>
       <c r="K36" t="n">
-        <v>9.045918941497803</v>
+        <v>8.456470727920532</v>
       </c>
       <c r="L36" t="n">
-        <v>8.394542050361633</v>
+        <v>8.401708436012267</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.222094535827637</v>
+        <v>8.0670006275177</v>
       </c>
       <c r="C37" t="n">
-        <v>7.207141876220703</v>
+        <v>8.350829362869263</v>
       </c>
       <c r="D37" t="n">
-        <v>6.935314178466797</v>
+        <v>7.737847089767456</v>
       </c>
       <c r="E37" t="n">
-        <v>7.981155633926392</v>
+        <v>8.351763725280762</v>
       </c>
       <c r="F37" t="n">
-        <v>7.468495845794678</v>
+        <v>6.864144802093506</v>
       </c>
       <c r="G37" t="n">
-        <v>7.606602430343628</v>
+        <v>7.886451244354248</v>
       </c>
       <c r="H37" t="n">
-        <v>8.487349033355713</v>
+        <v>7.351875782012939</v>
       </c>
       <c r="I37" t="n">
-        <v>7.304906606674194</v>
+        <v>7.382265567779541</v>
       </c>
       <c r="J37" t="n">
-        <v>7.503358602523804</v>
+        <v>7.407733201980591</v>
       </c>
       <c r="K37" t="n">
-        <v>7.052020788192749</v>
+        <v>6.757406711578369</v>
       </c>
       <c r="L37" t="n">
-        <v>7.476843953132629</v>
+        <v>7.615731811523437</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.495384693145752</v>
+        <v>7.336396932601929</v>
       </c>
       <c r="C38" t="n">
-        <v>8.182141065597534</v>
+        <v>7.910918951034546</v>
       </c>
       <c r="D38" t="n">
-        <v>7.64649486541748</v>
+        <v>7.175316333770752</v>
       </c>
       <c r="E38" t="n">
-        <v>7.610586881637573</v>
+        <v>7.628536939620972</v>
       </c>
       <c r="F38" t="n">
-        <v>7.458982944488525</v>
+        <v>7.731828927993774</v>
       </c>
       <c r="G38" t="n">
-        <v>7.769200563430786</v>
+        <v>7.577199935913086</v>
       </c>
       <c r="H38" t="n">
-        <v>8.329283714294434</v>
+        <v>7.606616973876953</v>
       </c>
       <c r="I38" t="n">
-        <v>7.445729494094849</v>
+        <v>8.030540466308594</v>
       </c>
       <c r="J38" t="n">
-        <v>7.657570600509644</v>
+        <v>8.171179294586182</v>
       </c>
       <c r="K38" t="n">
-        <v>8.111378192901611</v>
+        <v>8.433539628982544</v>
       </c>
       <c r="L38" t="n">
-        <v>7.770675301551819</v>
+        <v>7.760207438468933</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>8.202147483825684</v>
+        <v>7.627553939819336</v>
       </c>
       <c r="C39" t="n">
-        <v>7.97523045539856</v>
+        <v>8.816530704498291</v>
       </c>
       <c r="D39" t="n">
-        <v>8.688875436782837</v>
+        <v>9.355176687240601</v>
       </c>
       <c r="E39" t="n">
-        <v>8.221582651138306</v>
+        <v>9.482839345932007</v>
       </c>
       <c r="F39" t="n">
-        <v>7.859999418258667</v>
+        <v>8.177180528640747</v>
       </c>
       <c r="G39" t="n">
-        <v>7.945242881774902</v>
+        <v>7.989609003067017</v>
       </c>
       <c r="H39" t="n">
-        <v>8.031005382537842</v>
+        <v>8.895477771759033</v>
       </c>
       <c r="I39" t="n">
-        <v>7.968189001083374</v>
+        <v>8.481418132781982</v>
       </c>
       <c r="J39" t="n">
-        <v>8.01454496383667</v>
+        <v>7.488046646118164</v>
       </c>
       <c r="K39" t="n">
-        <v>7.504359006881714</v>
+        <v>7.545853853225708</v>
       </c>
       <c r="L39" t="n">
-        <v>8.041117668151855</v>
+        <v>8.385968661308288</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.633543014526367</v>
+        <v>7.546857833862305</v>
       </c>
       <c r="C40" t="n">
-        <v>7.4071044921875</v>
+        <v>7.745349884033203</v>
       </c>
       <c r="D40" t="n">
-        <v>9.783039569854736</v>
+        <v>7.600215435028076</v>
       </c>
       <c r="E40" t="n">
-        <v>7.834045886993408</v>
+        <v>7.128961801528931</v>
       </c>
       <c r="F40" t="n">
-        <v>8.343255043029785</v>
+        <v>7.309483766555786</v>
       </c>
       <c r="G40" t="n">
-        <v>7.447995185852051</v>
+        <v>7.304518222808838</v>
       </c>
       <c r="H40" t="n">
-        <v>8.131731748580933</v>
+        <v>9.153668880462646</v>
       </c>
       <c r="I40" t="n">
-        <v>7.637062549591064</v>
+        <v>7.041183471679688</v>
       </c>
       <c r="J40" t="n">
-        <v>8.59458589553833</v>
+        <v>7.279033899307251</v>
       </c>
       <c r="K40" t="n">
-        <v>8.256461381912231</v>
+        <v>8.497404813766479</v>
       </c>
       <c r="L40" t="n">
-        <v>8.106882476806641</v>
+        <v>7.660667800903321</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.862924814224243</v>
+        <v>6.935493230819702</v>
       </c>
       <c r="C41" t="n">
-        <v>8.045484066009521</v>
+        <v>7.64564061164856</v>
       </c>
       <c r="D41" t="n">
-        <v>8.697342395782471</v>
+        <v>8.374733924865723</v>
       </c>
       <c r="E41" t="n">
-        <v>8.132746934890747</v>
+        <v>7.899940729141235</v>
       </c>
       <c r="F41" t="n">
-        <v>7.356242179870605</v>
+        <v>8.035109519958496</v>
       </c>
       <c r="G41" t="n">
-        <v>9.130192756652832</v>
+        <v>8.012164354324341</v>
       </c>
       <c r="H41" t="n">
-        <v>8.405593156814575</v>
+        <v>8.310899496078491</v>
       </c>
       <c r="I41" t="n">
-        <v>7.425050497055054</v>
+        <v>12.17358493804932</v>
       </c>
       <c r="J41" t="n">
-        <v>8.182660341262817</v>
+        <v>9.235944271087646</v>
       </c>
       <c r="K41" t="n">
-        <v>7.707852363586426</v>
+        <v>8.302869081497192</v>
       </c>
       <c r="L41" t="n">
-        <v>8.09460895061493</v>
+        <v>8.492638015747071</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>9.631425142288208</v>
+        <v>9.139700651168823</v>
       </c>
       <c r="C42" t="n">
-        <v>8.28742790222168</v>
+        <v>8.666467189788818</v>
       </c>
       <c r="D42" t="n">
-        <v>8.763261318206787</v>
+        <v>7.637601375579834</v>
       </c>
       <c r="E42" t="n">
-        <v>8.899490356445312</v>
+        <v>7.860204696655273</v>
       </c>
       <c r="F42" t="n">
-        <v>7.622659206390381</v>
+        <v>7.802124261856079</v>
       </c>
       <c r="G42" t="n">
-        <v>7.263082027435303</v>
+        <v>9.427036762237549</v>
       </c>
       <c r="H42" t="n">
-        <v>8.379196643829346</v>
+        <v>7.329820871353149</v>
       </c>
       <c r="I42" t="n">
-        <v>7.999650478363037</v>
+        <v>7.544286251068115</v>
       </c>
       <c r="J42" t="n">
-        <v>9.139203310012817</v>
+        <v>8.758691787719727</v>
       </c>
       <c r="K42" t="n">
-        <v>8.639495372772217</v>
+        <v>8.439487218856812</v>
       </c>
       <c r="L42" t="n">
-        <v>8.462489175796509</v>
+        <v>8.260542106628417</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.429663419723511</v>
+        <v>7.87542200088501</v>
       </c>
       <c r="C43" t="n">
-        <v>7.706419944763184</v>
+        <v>7.652498483657837</v>
       </c>
       <c r="D43" t="n">
-        <v>7.435655117034912</v>
+        <v>8.951696872711182</v>
       </c>
       <c r="E43" t="n">
-        <v>8.483417987823486</v>
+        <v>8.709313154220581</v>
       </c>
       <c r="F43" t="n">
-        <v>9.039451837539673</v>
+        <v>8.022562980651855</v>
       </c>
       <c r="G43" t="n">
-        <v>7.260075569152832</v>
+        <v>7.038549423217773</v>
       </c>
       <c r="H43" t="n">
-        <v>8.99357008934021</v>
+        <v>7.730806112289429</v>
       </c>
       <c r="I43" t="n">
-        <v>7.656076431274414</v>
+        <v>7.35274863243103</v>
       </c>
       <c r="J43" t="n">
-        <v>8.141812801361084</v>
+        <v>8.512787580490112</v>
       </c>
       <c r="K43" t="n">
-        <v>8.262483596801758</v>
+        <v>8.087877511978149</v>
       </c>
       <c r="L43" t="n">
-        <v>8.040862679481506</v>
+        <v>7.993426275253296</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>7.010759830474854</v>
+        <v>7.13931941986084</v>
       </c>
       <c r="C44" t="n">
-        <v>7.196259498596191</v>
+        <v>6.591263294219971</v>
       </c>
       <c r="D44" t="n">
-        <v>7.281542539596558</v>
+        <v>6.720370054244995</v>
       </c>
       <c r="E44" t="n">
-        <v>6.684591770172119</v>
+        <v>6.465327262878418</v>
       </c>
       <c r="F44" t="n">
-        <v>7.199328660964966</v>
+        <v>6.552465677261353</v>
       </c>
       <c r="G44" t="n">
-        <v>7.117980480194092</v>
+        <v>7.170871257781982</v>
       </c>
       <c r="H44" t="n">
-        <v>6.762430191040039</v>
+        <v>7.983203411102295</v>
       </c>
       <c r="I44" t="n">
-        <v>6.955387592315674</v>
+        <v>8.292902946472168</v>
       </c>
       <c r="J44" t="n">
-        <v>7.678496122360229</v>
+        <v>6.615877628326416</v>
       </c>
       <c r="K44" t="n">
-        <v>6.920485734939575</v>
+        <v>6.877624273300171</v>
       </c>
       <c r="L44" t="n">
-        <v>7.080726242065429</v>
+        <v>7.040922522544861</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.738626956939697</v>
+        <v>8.381680488586426</v>
       </c>
       <c r="C45" t="n">
-        <v>9.736643075942993</v>
+        <v>10.26279854774475</v>
       </c>
       <c r="D45" t="n">
-        <v>8.584111928939819</v>
+        <v>9.276869535446167</v>
       </c>
       <c r="E45" t="n">
-        <v>8.947671890258789</v>
+        <v>9.062913179397583</v>
       </c>
       <c r="F45" t="n">
-        <v>8.875887393951416</v>
+        <v>10.01889657974243</v>
       </c>
       <c r="G45" t="n">
-        <v>8.538702487945557</v>
+        <v>10.23733353614807</v>
       </c>
       <c r="H45" t="n">
-        <v>9.578065156936646</v>
+        <v>9.865309000015259</v>
       </c>
       <c r="I45" t="n">
-        <v>8.517769575119019</v>
+        <v>10.15560555458069</v>
       </c>
       <c r="J45" t="n">
-        <v>9.263051509857178</v>
+        <v>9.619962930679321</v>
       </c>
       <c r="K45" t="n">
-        <v>10.21395564079285</v>
+        <v>9.580560922622681</v>
       </c>
       <c r="L45" t="n">
-        <v>9.099448561668396</v>
+        <v>9.646193027496338</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>8.888305425643921</v>
+        <v>7.532878875732422</v>
       </c>
       <c r="C46" t="n">
-        <v>7.661599159240723</v>
+        <v>8.338776350021362</v>
       </c>
       <c r="D46" t="n">
-        <v>8.425508260726929</v>
+        <v>7.344401836395264</v>
       </c>
       <c r="E46" t="n">
-        <v>9.297789335250854</v>
+        <v>8.169859647750854</v>
       </c>
       <c r="F46" t="n">
-        <v>7.422077655792236</v>
+        <v>8.822012424468994</v>
       </c>
       <c r="G46" t="n">
-        <v>8.302073001861572</v>
+        <v>8.57819390296936</v>
       </c>
       <c r="H46" t="n">
-        <v>7.65007472038269</v>
+        <v>8.183703184127808</v>
       </c>
       <c r="I46" t="n">
-        <v>9.656905889511108</v>
+        <v>8.585662603378296</v>
       </c>
       <c r="J46" t="n">
-        <v>8.175733327865601</v>
+        <v>7.726380109786987</v>
       </c>
       <c r="K46" t="n">
-        <v>7.293494701385498</v>
+        <v>8.913304328918457</v>
       </c>
       <c r="L46" t="n">
-        <v>8.277356147766113</v>
+        <v>8.21951732635498</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.954187154769897</v>
+        <v>8.958441734313965</v>
       </c>
       <c r="C47" t="n">
-        <v>8.567678689956665</v>
+        <v>8.444014549255371</v>
       </c>
       <c r="D47" t="n">
-        <v>9.948569536209106</v>
+        <v>8.533295154571533</v>
       </c>
       <c r="E47" t="n">
-        <v>8.954164266586304</v>
+        <v>9.89896559715271</v>
       </c>
       <c r="F47" t="n">
-        <v>8.377180576324463</v>
+        <v>8.333303689956665</v>
       </c>
       <c r="G47" t="n">
-        <v>9.163599491119385</v>
+        <v>8.61855936050415</v>
       </c>
       <c r="H47" t="n">
-        <v>8.070502281188965</v>
+        <v>8.603134155273438</v>
       </c>
       <c r="I47" t="n">
-        <v>8.670438289642334</v>
+        <v>9.091821670532227</v>
       </c>
       <c r="J47" t="n">
-        <v>8.460958003997803</v>
+        <v>9.61299729347229</v>
       </c>
       <c r="K47" t="n">
-        <v>9.40253210067749</v>
+        <v>9.896167039871216</v>
       </c>
       <c r="L47" t="n">
-        <v>8.856981039047241</v>
+        <v>8.999070024490356</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>8.053032636642456</v>
+        <v>7.428078413009644</v>
       </c>
       <c r="C48" t="n">
-        <v>6.868119239807129</v>
+        <v>7.184692621231079</v>
       </c>
       <c r="D48" t="n">
-        <v>7.549360036849976</v>
+        <v>6.371250629425049</v>
       </c>
       <c r="E48" t="n">
-        <v>7.693933486938477</v>
+        <v>6.295488119125366</v>
       </c>
       <c r="F48" t="n">
-        <v>6.919995307922363</v>
+        <v>7.541258573532104</v>
       </c>
       <c r="G48" t="n">
-        <v>6.653666973114014</v>
+        <v>8.774626016616821</v>
       </c>
       <c r="H48" t="n">
-        <v>6.97034740447998</v>
+        <v>6.514883279800415</v>
       </c>
       <c r="I48" t="n">
-        <v>6.724490165710449</v>
+        <v>8.199082851409912</v>
       </c>
       <c r="J48" t="n">
-        <v>6.616762161254883</v>
+        <v>8.602070808410645</v>
       </c>
       <c r="K48" t="n">
-        <v>7.333395719528198</v>
+        <v>7.612135410308838</v>
       </c>
       <c r="L48" t="n">
-        <v>7.138310313224792</v>
+        <v>7.452356672286987</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.680483818054199</v>
+        <v>7.858949422836304</v>
       </c>
       <c r="C49" t="n">
-        <v>7.148890972137451</v>
+        <v>7.277439832687378</v>
       </c>
       <c r="D49" t="n">
-        <v>7.779239416122437</v>
+        <v>7.990689277648926</v>
       </c>
       <c r="E49" t="n">
-        <v>8.590014934539795</v>
+        <v>8.24405574798584</v>
       </c>
       <c r="F49" t="n">
-        <v>7.803103685379028</v>
+        <v>7.693475484848022</v>
       </c>
       <c r="G49" t="n">
-        <v>7.484404563903809</v>
+        <v>7.159866333007812</v>
       </c>
       <c r="H49" t="n">
-        <v>8.069402694702148</v>
+        <v>7.706417798995972</v>
       </c>
       <c r="I49" t="n">
-        <v>6.979196548461914</v>
+        <v>8.055017232894897</v>
       </c>
       <c r="J49" t="n">
-        <v>8.254093170166016</v>
+        <v>7.500000715255737</v>
       </c>
       <c r="K49" t="n">
-        <v>6.943437099456787</v>
+        <v>7.592665433883667</v>
       </c>
       <c r="L49" t="n">
-        <v>7.673226690292358</v>
+        <v>7.707857728004456</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>8.561709642410278</v>
+        <v>7.753711938858032</v>
       </c>
       <c r="C50" t="n">
-        <v>8.387161731719971</v>
+        <v>8.626070976257324</v>
       </c>
       <c r="D50" t="n">
-        <v>8.996060848236084</v>
+        <v>7.411102533340454</v>
       </c>
       <c r="E50" t="n">
-        <v>8.903344392776489</v>
+        <v>8.663438081741333</v>
       </c>
       <c r="F50" t="n">
-        <v>9.705240249633789</v>
+        <v>8.060437440872192</v>
       </c>
       <c r="G50" t="n">
-        <v>8.140298366546631</v>
+        <v>8.482973575592041</v>
       </c>
       <c r="H50" t="n">
-        <v>9.536664485931396</v>
+        <v>8.948208093643188</v>
       </c>
       <c r="I50" t="n">
-        <v>8.865473747253418</v>
+        <v>8.99014687538147</v>
       </c>
       <c r="J50" t="n">
-        <v>8.672430276870728</v>
+        <v>8.813531875610352</v>
       </c>
       <c r="K50" t="n">
-        <v>9.372590065002441</v>
+        <v>9.172121047973633</v>
       </c>
       <c r="L50" t="n">
-        <v>8.914097380638122</v>
+        <v>8.492174243927002</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.862556219100952</v>
+        <v>7.337788105010986</v>
       </c>
       <c r="C51" t="n">
-        <v>7.335877180099487</v>
+        <v>6.901898145675659</v>
       </c>
       <c r="D51" t="n">
-        <v>8.236537456512451</v>
+        <v>7.552239894866943</v>
       </c>
       <c r="E51" t="n">
-        <v>7.608197212219238</v>
+        <v>7.09243106842041</v>
       </c>
       <c r="F51" t="n">
-        <v>7.771285772323608</v>
+        <v>7.568258285522461</v>
       </c>
       <c r="G51" t="n">
-        <v>7.200237274169922</v>
+        <v>7.629546403884888</v>
       </c>
       <c r="H51" t="n">
-        <v>6.52419376373291</v>
+        <v>7.779144048690796</v>
       </c>
       <c r="I51" t="n">
-        <v>7.938241958618164</v>
+        <v>6.828595876693726</v>
       </c>
       <c r="J51" t="n">
-        <v>7.067493677139282</v>
+        <v>7.932265281677246</v>
       </c>
       <c r="K51" t="n">
-        <v>7.721807241439819</v>
+        <v>7.337785720825195</v>
       </c>
       <c r="L51" t="n">
-        <v>7.526642775535583</v>
+        <v>7.395995283126831</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.230548839569092</v>
+        <v>8.203201370239258</v>
       </c>
       <c r="C52" t="n">
-        <v>8.265544176101685</v>
+        <v>8.086299691200256</v>
       </c>
       <c r="D52" t="n">
-        <v>8.422323718070984</v>
+        <v>8.395695285797119</v>
       </c>
       <c r="E52" t="n">
-        <v>8.305891046524048</v>
+        <v>8.193042407035827</v>
       </c>
       <c r="F52" t="n">
-        <v>8.341697058677674</v>
+        <v>8.187114934921265</v>
       </c>
       <c r="G52" t="n">
-        <v>8.148484773635865</v>
+        <v>8.175333194732666</v>
       </c>
       <c r="H52" t="n">
-        <v>8.380489683151245</v>
+        <v>8.246056938171387</v>
       </c>
       <c r="I52" t="n">
-        <v>8.28685986995697</v>
+        <v>8.374254980087279</v>
       </c>
       <c r="J52" t="n">
-        <v>8.375670561790466</v>
+        <v>8.288686656951905</v>
       </c>
       <c r="K52" t="n">
-        <v>8.348359007835388</v>
+        <v>8.569768767356873</v>
       </c>
       <c r="L52" t="n">
-        <v>8.310586873531342</v>
+        <v>8.271945422649384</v>
       </c>
     </row>
   </sheetData>
